--- a/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B02_Normal_2.xlsx
+++ b/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B02_Normal_2.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1865502853357017</v>
+        <v>0.1865600545781031</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9027069616915873</v>
+        <v>0.9025130183448353</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.329790079151363</v>
+        <v>1.329840539349983</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.333486823954726</v>
+        <v>5.331086360382172</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.042760034830393</v>
+        <v>6.039954809969425</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>9.774211633003286</v>
+        <v>9.635797748144768</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>10.47404150664014</v>
+        <v>10.47449632497913</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>10.50943319366649</v>
+        <v>10.50475136658863</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>12.33737930054762</v>
+        <v>12.33786735892068</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>1.112358201660258</v>
+        <v>1.112431640076021</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.062777698332418</v>
+        <v>1.063099514135826</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5772589909199825</v>
+        <v>0.5792498871576799</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>15.92122532206255</v>
+        <v>16.08614487448754</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>15.92244207042752</v>
+        <v>15.9224055805709</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>15.95062527901377</v>
+        <v>15.94907264007682</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>16.68125211750191</v>
+        <v>16.68150359318814</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>17.13662195006867</v>
+        <v>17.13699864778113</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>17.65643758803501</v>
+        <v>17.65606000717672</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>17.726221843046</v>
+        <v>17.72686803633449</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>17.81936612530993</v>
+        <v>17.81944109171629</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>17.83069852722052</v>
+        <v>17.82989940170764</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>17.91045501285387</v>
+        <v>17.91105143658421</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>18.11075800455528</v>
+        <v>18.11063187715624</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>18.25333437977661</v>
+        <v>18.25347872265014</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>18.31313623191253</v>
+        <v>18.31300880162258</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>18.19251281614148</v>
+        <v>18.18374248726346</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>18.43101520147438</v>
+        <v>18.43115021407112</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>18.5685952563802</v>
+        <v>18.56838849707095</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>18.58008141167307</v>
+        <v>18.58191783635835</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>18.83955821569582</v>
+        <v>18.84045488162381</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>18.7683839298948</v>
+        <v>18.76887581351305</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>18.73776743207468</v>
+        <v>18.74229667334115</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>18.54743048859889</v>
+        <v>18.54653760366034</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>18.15252804766378</v>
+        <v>18.15454817016082</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>18.08003792003841</v>
+        <v>18.08007013293001</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>18.0508829171354</v>
+        <v>18.04915627873921</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.7490806393877</v>
+        <v>17.74861576103778</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>17.81814662802715</v>
+        <v>17.79881074691802</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99225470919088</v>
+        <v>17.97859383075771</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>18.04864477364506</v>
+        <v>18.04209307204975</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>18.06393349092241</v>
+        <v>18.05583693465113</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>18.26553935250956</v>
+        <v>18.26535630570529</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>18.25615665036968</v>
+        <v>18.25543714052691</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>18.32865305918012</v>
+        <v>18.35082486847733</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>18.22115293721825</v>
+        <v>18.31842442556919</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>18.33354581660341</v>
+        <v>18.3533122614999</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>18.33354581660341</v>
+        <v>18.3533122614999</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>5</v>
       </c>
       <c r="K67" t="n">
-        <v>19.39058911605064</v>
+        <v>18.98502910614225</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>19.39058911605064</v>
+        <v>18.98502910614225</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>5</v>
       </c>
       <c r="K69" t="n">
-        <v>19.39058911605064</v>
+        <v>18.98502910614225</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>21.66404939438216</v>
+        <v>20.94651363125861</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>21.66404939438216</v>
+        <v>20.94651363125861</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="K72" t="n">
-        <v>22.14156626639458</v>
+        <v>21.90771317294598</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>25.26172031879001</v>
+        <v>24.74440899984982</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>6</v>
       </c>
       <c r="K74" t="n">
-        <v>25.97044060644363</v>
+        <v>26.03528585662074</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>26.11646230122699</v>
+        <v>26.22332903865059</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5580719708790981</v>
+        <v>0.5533339776287334</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>0.6100276373100441</v>
+        <v>0.6055200912820897</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>29.6365389211996</v>
+        <v>30.07087889291999</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>11</v>
       </c>
       <c r="K79" t="n">
-        <v>35.12420270964578</v>
+        <v>35.02754103242006</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>11</v>
       </c>
       <c r="K80" t="n">
-        <v>47.73271048949695</v>
+        <v>47.65226065884217</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>11</v>
       </c>
       <c r="K81" t="n">
-        <v>13.88133089435786</v>
+        <v>14.55183722232734</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>11</v>
       </c>
       <c r="K82" t="n">
-        <v>13.88133089435786</v>
+        <v>14.55183722232734</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>11</v>
       </c>
       <c r="K83" t="n">
-        <v>13.74166483511477</v>
+        <v>13.74243038787666</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="K84" t="n">
-        <v>13.77039253026818</v>
+        <v>13.76647967121961</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>11</v>
       </c>
       <c r="K85" t="n">
-        <v>13.91522883364549</v>
+        <v>13.89679213949339</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>11</v>
       </c>
       <c r="K86" t="n">
-        <v>14.15464986399265</v>
+        <v>14.14279892011348</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>11</v>
       </c>
       <c r="K87" t="n">
-        <v>14.15464986399265</v>
+        <v>14.14279892011348</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>11</v>
       </c>
       <c r="K88" t="n">
-        <v>14.15600295909167</v>
+        <v>14.1581575436393</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>11</v>
       </c>
       <c r="K89" t="n">
-        <v>14.87323432868604</v>
+        <v>14.8095600580859</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>11</v>
       </c>
       <c r="K90" t="n">
-        <v>15.96753192524295</v>
+        <v>15.92196134409564</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>11</v>
       </c>
       <c r="K91" t="n">
-        <v>17.21262387202559</v>
+        <v>16.85058333291669</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>11</v>
       </c>
       <c r="K92" t="n">
-        <v>20.77772854824513</v>
+        <v>20.35256474515269</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>11</v>
       </c>
       <c r="K93" t="n">
-        <v>22.67156069266465</v>
+        <v>22.68934257474131</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>11</v>
       </c>
       <c r="K94" t="n">
-        <v>6.348076425982764</v>
+        <v>6.401630356070631</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>11</v>
       </c>
       <c r="K95" t="n">
-        <v>6.078940762221635</v>
+        <v>6.097566293414858</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>11</v>
       </c>
       <c r="K96" t="n">
-        <v>5.824656068897504</v>
+        <v>5.827217142635461</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>11</v>
       </c>
       <c r="K97" t="n">
-        <v>5.778316721224879</v>
+        <v>5.776805824152891</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>11</v>
       </c>
       <c r="K98" t="n">
-        <v>5.8109734643236</v>
+        <v>5.808076848170203</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>11</v>
       </c>
       <c r="K99" t="n">
-        <v>5.827809132970579</v>
+        <v>5.842033865578964</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>11</v>
       </c>
       <c r="K100" t="n">
-        <v>5.948662981977272</v>
+        <v>5.944103002732143</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>11</v>
       </c>
       <c r="K101" t="n">
-        <v>5.948662981977272</v>
+        <v>5.973154623155878</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>11</v>
       </c>
       <c r="K102" t="n">
-        <v>5.948662981977272</v>
+        <v>5.973154623155878</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>11</v>
       </c>
       <c r="K103" t="n">
-        <v>6.026336446143675</v>
+        <v>6.02347651671986</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>11</v>
       </c>
       <c r="K104" t="n">
-        <v>6.136141703921297</v>
+        <v>6.136200571509163</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>11</v>
       </c>
       <c r="K105" t="n">
-        <v>6.139347991062152</v>
+        <v>6.136200571509163</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>11</v>
       </c>
       <c r="K106" t="n">
-        <v>6.139347991062152</v>
+        <v>6.136200571509163</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>11</v>
       </c>
       <c r="K107" t="n">
-        <v>6.242827500333878</v>
+        <v>6.23879156291939</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>11</v>
       </c>
       <c r="K108" t="n">
-        <v>6.242827500333878</v>
+        <v>6.23879156291939</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>11</v>
       </c>
       <c r="K109" t="n">
-        <v>6.299094299756129</v>
+        <v>6.297864219631516</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="K110" t="n">
-        <v>6.299094299756129</v>
+        <v>6.297864219631516</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>11</v>
       </c>
       <c r="K111" t="n">
-        <v>6.297187999546243</v>
+        <v>6.299777102226653</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>11</v>
       </c>
       <c r="K112" t="n">
-        <v>6.261492124280681</v>
+        <v>6.265137915896519</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>11</v>
       </c>
       <c r="K113" t="n">
-        <v>6.261492124280681</v>
+        <v>6.265137915896519</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>11</v>
       </c>
       <c r="K114" t="n">
-        <v>6.261492124280681</v>
+        <v>6.258922483035779</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>11</v>
       </c>
       <c r="K115" t="n">
-        <v>6.255516650809001</v>
+        <v>6.213053887930298</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>11</v>
       </c>
       <c r="K116" t="n">
-        <v>6.205840041580825</v>
+        <v>6.206277747060963</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>11</v>
       </c>
       <c r="K117" t="n">
-        <v>6.092692575513145</v>
+        <v>6.097839178954078</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>11</v>
       </c>
       <c r="K118" t="n">
-        <v>6.092692575513145</v>
+        <v>6.093946020521035</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>11</v>
       </c>
       <c r="K119" t="n">
-        <v>6.025643897952638</v>
+        <v>6.029748741767092</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>11</v>
       </c>
       <c r="K120" t="n">
-        <v>5.970454547763208</v>
+        <v>5.970738766408267</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>11</v>
       </c>
       <c r="K121" t="n">
-        <v>5.976657136631865</v>
+        <v>5.974389393878274</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>11</v>
       </c>
       <c r="K122" t="n">
-        <v>6.032355149831399</v>
+        <v>6.031160204473665</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>11</v>
       </c>
       <c r="K123" t="n">
-        <v>6.156813791521671</v>
+        <v>6.152260442541584</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>11</v>
       </c>
       <c r="K124" t="n">
-        <v>6.173913262796976</v>
+        <v>6.152260442541584</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>11</v>
       </c>
       <c r="K125" t="n">
-        <v>6.173913262796976</v>
+        <v>6.152260442541584</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>11</v>
       </c>
       <c r="K126" t="n">
-        <v>6.280916741641971</v>
+        <v>6.277603612598189</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>11</v>
       </c>
       <c r="K127" t="n">
-        <v>6.35776337409236</v>
+        <v>6.355772387830935</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>11</v>
       </c>
       <c r="K128" t="n">
-        <v>6.424870266054</v>
+        <v>6.416283450523281</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>11</v>
       </c>
       <c r="K129" t="n">
-        <v>6.443102258093636</v>
+        <v>6.447504354046735</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>11</v>
       </c>
       <c r="K130" t="n">
-        <v>6.378624851225294</v>
+        <v>6.396148672774477</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="K131" t="n">
-        <v>6.011175728344443</v>
+        <v>5.9447234905927</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>11</v>
       </c>
       <c r="K132" t="n">
-        <v>5.629913836015289</v>
+        <v>5.536522260433312</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>11</v>
       </c>
       <c r="K133" t="n">
-        <v>5.515452821174803</v>
+        <v>5.536522260433312</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>11</v>
       </c>
       <c r="K134" t="n">
-        <v>5.515452821174803</v>
+        <v>5.518666092689419</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>11</v>
       </c>
       <c r="K135" t="n">
-        <v>5.340254689474807</v>
+        <v>5.349020209852179</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>11</v>
       </c>
       <c r="K136" t="n">
-        <v>5.402189197777472</v>
+        <v>5.389434556435008</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>11</v>
       </c>
       <c r="K137" t="n">
-        <v>5.402189197777472</v>
+        <v>5.463160466577598</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>11</v>
       </c>
       <c r="K138" t="n">
-        <v>5.763505445035396</v>
+        <v>5.757361352583624</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>11</v>
       </c>
       <c r="K139" t="n">
-        <v>5.805375504797411</v>
+        <v>5.800863004662847</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>11</v>
       </c>
       <c r="K140" t="n">
-        <v>5.822129207168561</v>
+        <v>5.821208552593205</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>11</v>
       </c>
       <c r="K141" t="n">
-        <v>5.713655168056981</v>
+        <v>5.722718862186042</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>11</v>
       </c>
       <c r="K142" t="n">
-        <v>5.658062444909339</v>
+        <v>5.663779831107326</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>11</v>
       </c>
       <c r="K143" t="n">
-        <v>5.594062058535003</v>
+        <v>5.599836593369151</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>11</v>
       </c>
       <c r="K144" t="n">
-        <v>5.54167211003111</v>
+        <v>5.547532444968658</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>11</v>
       </c>
       <c r="K145" t="n">
-        <v>5.515682624903937</v>
+        <v>5.518156790814201</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>11</v>
       </c>
       <c r="K146" t="n">
-        <v>5.509231015372827</v>
+        <v>5.509742528910757</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>11</v>
       </c>
       <c r="K147" t="n">
-        <v>5.509613874801729</v>
+        <v>5.509815689314163</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>11</v>
       </c>
       <c r="K148" t="n">
-        <v>5.509052047855538</v>
+        <v>5.511953596958141</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>11</v>
       </c>
       <c r="K149" t="n">
-        <v>5.527733606238759</v>
+        <v>5.523042368862513</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>11</v>
       </c>
       <c r="K150" t="n">
-        <v>5.707060779857225</v>
+        <v>5.703444878523909</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>11</v>
       </c>
       <c r="K151" t="n">
-        <v>5.772635834653211</v>
+        <v>5.768483895201498</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>11</v>
       </c>
       <c r="K152" t="n">
-        <v>5.776166080134412</v>
+        <v>5.77294640691072</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>11</v>
       </c>
       <c r="K153" t="n">
-        <v>5.776166080134412</v>
+        <v>5.77294640691072</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>11</v>
       </c>
       <c r="K154" t="n">
-        <v>5.74775054505161</v>
+        <v>5.74728394335339</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>11</v>
       </c>
       <c r="K155" t="n">
-        <v>5.726518369063268</v>
+        <v>5.724788181585789</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>11</v>
       </c>
       <c r="K156" t="n">
-        <v>5.650778902908321</v>
+        <v>5.606965816150596</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>11</v>
       </c>
       <c r="K157" t="n">
-        <v>5.518397574667046</v>
+        <v>5.531263597306034</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>11</v>
       </c>
       <c r="K158" t="n">
-        <v>5.338850019871813</v>
+        <v>5.342186881612034</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>11</v>
       </c>
       <c r="K159" t="n">
-        <v>5.338850019871813</v>
+        <v>5.342186881612034</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>11</v>
       </c>
       <c r="K160" t="n">
-        <v>5.318446183448564</v>
+        <v>5.318334149848797</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>11</v>
       </c>
       <c r="K161" t="n">
-        <v>5.234106663439335</v>
+        <v>5.18692569461091</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>11</v>
       </c>
       <c r="K162" t="n">
-        <v>5.167099803931877</v>
+        <v>5.175887955228201</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>11</v>
       </c>
       <c r="K163" t="n">
-        <v>5.074456284822193</v>
+        <v>5.073894588920303</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>11</v>
       </c>
       <c r="K164" t="n">
-        <v>5.003695358431928</v>
+        <v>4.970435180686554</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>11</v>
       </c>
       <c r="K165" t="n">
-        <v>4.966092906623629</v>
+        <v>4.967802877101163</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>11</v>
       </c>
       <c r="K166" t="n">
-        <v>4.961511895082562</v>
+        <v>4.962172871957925</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>11</v>
       </c>
       <c r="K167" t="n">
-        <v>4.954490091396989</v>
+        <v>4.956001463430384</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>11</v>
       </c>
       <c r="K168" t="n">
-        <v>4.954089082489625</v>
+        <v>4.953312816619061</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>11</v>
       </c>
       <c r="K169" t="n">
-        <v>4.969505243281092</v>
+        <v>4.971024056022783</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>11</v>
       </c>
       <c r="K170" t="n">
-        <v>4.971395355298045</v>
+        <v>4.971222405844165</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>11</v>
       </c>
       <c r="K171" t="n">
-        <v>4.973192503185665</v>
+        <v>4.970695264374353</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>11</v>
       </c>
       <c r="K172" t="n">
-        <v>4.924555670984629</v>
+        <v>4.934570540703212</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>11</v>
       </c>
       <c r="K173" t="n">
-        <v>4.924555670984629</v>
+        <v>4.934570540703212</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>11</v>
       </c>
       <c r="K174" t="n">
-        <v>4.797111306033184</v>
+        <v>4.808777506145151</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>11</v>
       </c>
       <c r="K175" t="n">
-        <v>4.586043869158029</v>
+        <v>4.584894577284373</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>11</v>
       </c>
       <c r="K176" t="n">
-        <v>4.550561726913672</v>
+        <v>4.554310821530987</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>11</v>
       </c>
       <c r="K177" t="n">
-        <v>4.539191009314511</v>
+        <v>4.536221337424327</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>11</v>
       </c>
       <c r="K178" t="n">
-        <v>4.543649803142861</v>
+        <v>4.539765112401659</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>11</v>
       </c>
       <c r="K179" t="n">
-        <v>4.57070564535683</v>
+        <v>4.570086475964073</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>11</v>
       </c>
       <c r="K180" t="n">
-        <v>4.754113373438671</v>
+        <v>4.743151431886276</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>11</v>
       </c>
       <c r="K181" t="n">
-        <v>4.765895196618014</v>
+        <v>4.806128263720731</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>11</v>
       </c>
       <c r="K182" t="n">
-        <v>4.931130712449697</v>
+        <v>4.923659421806253</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>11</v>
       </c>
       <c r="K183" t="n">
-        <v>4.938780133806848</v>
+        <v>4.962563369455107</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>11</v>
       </c>
       <c r="K184" t="n">
-        <v>4.981814202633253</v>
+        <v>4.981359412775992</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>11</v>
       </c>
       <c r="K185" t="n">
-        <v>4.981814202633253</v>
+        <v>4.981359412775992</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>11</v>
       </c>
       <c r="K186" t="n">
-        <v>4.96797197419574</v>
+        <v>4.970702864755816</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>11</v>
       </c>
       <c r="K187" t="n">
-        <v>4.96797197419574</v>
+        <v>4.966413908558377</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>11</v>
       </c>
       <c r="K188" t="n">
-        <v>4.940998233710269</v>
+        <v>4.945987167403445</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>11</v>
       </c>
       <c r="K189" t="n">
-        <v>4.932646285698764</v>
+        <v>4.938530182139829</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>11</v>
       </c>
       <c r="K190" t="n">
-        <v>4.881260081913819</v>
+        <v>4.892872537922536</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>11</v>
       </c>
       <c r="K191" t="n">
-        <v>4.881260081913819</v>
+        <v>4.892872537922536</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>11</v>
       </c>
       <c r="K192" t="n">
-        <v>4.794296664854921</v>
+        <v>4.805981966529709</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>11</v>
       </c>
       <c r="K193" t="n">
-        <v>4.794296664854921</v>
+        <v>4.742176446565601</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>11</v>
       </c>
       <c r="K194" t="n">
-        <v>4.656133677744146</v>
+        <v>4.666460444036578</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>11</v>
       </c>
       <c r="K195" t="n">
-        <v>4.60685191542309</v>
+        <v>4.613041718904388</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>11</v>
       </c>
       <c r="K196" t="n">
-        <v>4.600406641594655</v>
+        <v>4.60551242798371</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>11</v>
       </c>
       <c r="K197" t="n">
-        <v>4.600406641594655</v>
+        <v>4.60551242798371</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>11</v>
       </c>
       <c r="K198" t="n">
-        <v>4.57132319617785</v>
+        <v>4.55562242318247</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>11</v>
       </c>
       <c r="K199" t="n">
-        <v>4.553553709335127</v>
+        <v>4.55562242318247</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>11</v>
       </c>
       <c r="K200" t="n">
-        <v>4.553553709335127</v>
+        <v>4.55562242318247</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>11</v>
       </c>
       <c r="K201" t="n">
-        <v>4.684531204800618</v>
+        <v>4.673710198734463</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>11</v>
       </c>
       <c r="K202" t="n">
-        <v>4.811672152732666</v>
+        <v>4.814485079586134</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>11</v>
       </c>
       <c r="K203" t="n">
-        <v>4.873384018326188</v>
+        <v>4.864976448301955</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>11</v>
       </c>
       <c r="K204" t="n">
-        <v>4.873384018326188</v>
+        <v>4.864976448301955</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>11</v>
       </c>
       <c r="K205" t="n">
-        <v>4.920002023269015</v>
+        <v>4.934974448339537</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>11</v>
       </c>
       <c r="K206" t="n">
-        <v>4.952542132501267</v>
+        <v>4.950637516415615</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>11</v>
       </c>
       <c r="K207" t="n">
-        <v>4.957926678907644</v>
+        <v>4.957122020010996</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>11</v>
       </c>
       <c r="K208" t="n">
-        <v>4.899684923085393</v>
+        <v>4.905743975547935</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>11</v>
       </c>
       <c r="K209" t="n">
-        <v>4.862147018695466</v>
+        <v>4.871042983340159</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>11</v>
       </c>
       <c r="K210" t="n">
-        <v>4.698215921956132</v>
+        <v>4.712230412033672</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>11</v>
       </c>
       <c r="K211" t="n">
-        <v>4.680944303250237</v>
+        <v>4.625336978757067</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>11</v>
       </c>
       <c r="K212" t="n">
-        <v>4.61144228403766</v>
+        <v>4.625336978757067</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>11</v>
       </c>
       <c r="K213" t="n">
-        <v>4.594443802100583</v>
+        <v>4.606603922760104</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>11</v>
       </c>
       <c r="K214" t="n">
-        <v>4.594443802100583</v>
+        <v>4.606603922760104</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>11</v>
       </c>
       <c r="K215" t="n">
-        <v>4.594443802100583</v>
+        <v>4.54820683519569</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>11</v>
       </c>
       <c r="K216" t="n">
-        <v>4.484930887844632</v>
+        <v>4.492994590832175</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>11</v>
       </c>
       <c r="K217" t="n">
-        <v>4.407950002624006</v>
+        <v>4.417281567606321</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>11</v>
       </c>
       <c r="K218" t="n">
-        <v>4.407950002624006</v>
+        <v>4.417281567606321</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>11</v>
       </c>
       <c r="K219" t="n">
-        <v>4.354660283813772</v>
+        <v>4.360905692179425</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>11</v>
       </c>
       <c r="K220" t="n">
-        <v>4.316878582979106</v>
+        <v>4.315742618854717</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>11</v>
       </c>
       <c r="K221" t="n">
-        <v>4.339812030613509</v>
+        <v>4.333537276938348</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>11</v>
       </c>
       <c r="K222" t="n">
-        <v>4.39161569828178</v>
+        <v>4.385115302976289</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>11</v>
       </c>
       <c r="K223" t="n">
-        <v>4.499931404007591</v>
+        <v>4.505166930853544</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>11</v>
       </c>
       <c r="K224" t="n">
-        <v>4.829819403023957</v>
+        <v>4.81671414773008</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>11</v>
       </c>
       <c r="K225" t="n">
-        <v>5.121903748059097</v>
+        <v>5.105960297663039</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>11</v>
       </c>
       <c r="K226" t="n">
-        <v>5.201563945194972</v>
+        <v>5.191310654024108</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>11</v>
       </c>
       <c r="K227" t="n">
-        <v>5.231080437320639</v>
+        <v>5.231367614063491</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>11</v>
       </c>
       <c r="K228" t="n">
-        <v>5.231080437320639</v>
+        <v>5.230912772737371</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>11</v>
       </c>
       <c r="K229" t="n">
-        <v>5.219653968950234</v>
+        <v>5.211126228682526</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>11</v>
       </c>
       <c r="K230" t="n">
-        <v>5.206459386911871</v>
+        <v>5.204180518502039</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>11</v>
       </c>
       <c r="K231" t="n">
-        <v>5.206459386911871</v>
+        <v>5.204180518502039</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>11</v>
       </c>
       <c r="K232" t="n">
-        <v>4.989438251565988</v>
+        <v>5.00600672102353</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>11</v>
       </c>
       <c r="K233" t="n">
-        <v>4.900300390362581</v>
+        <v>4.923029805233028</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>11</v>
       </c>
       <c r="K234" t="n">
-        <v>4.648535391356188</v>
+        <v>4.665211952909202</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>11</v>
       </c>
       <c r="K235" t="n">
-        <v>4.648535391356188</v>
+        <v>4.665211952909202</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>11</v>
       </c>
       <c r="K236" t="n">
-        <v>4.622624687946874</v>
+        <v>4.635871676490274</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>11</v>
       </c>
       <c r="K237" t="n">
-        <v>4.622624687946874</v>
+        <v>4.635871676490274</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>11</v>
       </c>
       <c r="K238" t="n">
-        <v>4.406694484653884</v>
+        <v>4.424428682338489</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>11</v>
       </c>
       <c r="K239" t="n">
-        <v>4.271660086547803</v>
+        <v>4.285509671940753</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>11</v>
       </c>
       <c r="K240" t="n">
-        <v>4.109464617549209</v>
+        <v>4.073028071513384</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>11</v>
       </c>
       <c r="K241" t="n">
-        <v>3.98389791132499</v>
+        <v>3.974024440708728</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>11</v>
       </c>
       <c r="K242" t="n">
-        <v>3.889998595602655</v>
+        <v>3.885960216697364</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>11</v>
       </c>
       <c r="K243" t="n">
-        <v>3.87452493615409</v>
+        <v>3.87270999241685</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>11</v>
       </c>
       <c r="K244" t="n">
-        <v>3.891193544502435</v>
+        <v>3.887614122600454</v>
       </c>
     </row>
     <row r="245">
@@ -10486,7 +10486,7 @@
         <v>11</v>
       </c>
       <c r="K245" t="n">
-        <v>4.043585919493533</v>
+        <v>4.037440718867917</v>
       </c>
     </row>
     <row r="246">
@@ -10527,7 +10527,7 @@
         <v>11</v>
       </c>
       <c r="K246" t="n">
-        <v>4.074522416587977</v>
+        <v>4.069205377781238</v>
       </c>
     </row>
     <row r="247">
@@ -10568,7 +10568,7 @@
         <v>11</v>
       </c>
       <c r="K247" t="n">
-        <v>4.299321291415121</v>
+        <v>4.285381009111915</v>
       </c>
     </row>
     <row r="248">
@@ -10609,7 +10609,7 @@
         <v>11</v>
       </c>
       <c r="K248" t="n">
-        <v>4.374644973609595</v>
+        <v>4.362509043794709</v>
       </c>
     </row>
     <row r="249">
@@ -10650,7 +10650,7 @@
         <v>11</v>
       </c>
       <c r="K249" t="n">
-        <v>4.496790518703213</v>
+        <v>4.528645946274604</v>
       </c>
     </row>
     <row r="250">
@@ -10691,7 +10691,7 @@
         <v>11</v>
       </c>
       <c r="K250" t="n">
-        <v>4.550476422978299</v>
+        <v>4.582292803372609</v>
       </c>
     </row>
     <row r="251">
@@ -10732,7 +10732,7 @@
         <v>11</v>
       </c>
       <c r="K251" t="n">
-        <v>4.550476422978299</v>
+        <v>4.582292803372609</v>
       </c>
     </row>
     <row r="252">
@@ -10773,7 +10773,7 @@
         <v>11</v>
       </c>
       <c r="K252" t="n">
-        <v>4.70577795230737</v>
+        <v>4.698864650250515</v>
       </c>
     </row>
     <row r="253">
@@ -10814,7 +10814,7 @@
         <v>11</v>
       </c>
       <c r="K253" t="n">
-        <v>4.70577795230737</v>
+        <v>4.752886950442493</v>
       </c>
     </row>
     <row r="254">
@@ -10855,7 +10855,7 @@
         <v>11</v>
       </c>
       <c r="K254" t="n">
-        <v>4.914436875803528</v>
+        <v>4.903048838406642</v>
       </c>
     </row>
     <row r="255">
@@ -10896,7 +10896,7 @@
         <v>11</v>
       </c>
       <c r="K255" t="n">
-        <v>5.105450333867424</v>
+        <v>5.085490774542873</v>
       </c>
     </row>
     <row r="256">
@@ -10937,7 +10937,7 @@
         <v>11</v>
       </c>
       <c r="K256" t="n">
-        <v>5.247692925920606</v>
+        <v>5.225475141379467</v>
       </c>
     </row>
     <row r="257">
@@ -10978,7 +10978,7 @@
         <v>11</v>
       </c>
       <c r="K257" t="n">
-        <v>5.502778604715304</v>
+        <v>5.484455385653733</v>
       </c>
     </row>
     <row r="258">
@@ -11019,7 +11019,7 @@
         <v>11</v>
       </c>
       <c r="K258" t="n">
-        <v>5.502778604715304</v>
+        <v>5.484455385653733</v>
       </c>
     </row>
     <row r="259">
@@ -11060,7 +11060,7 @@
         <v>11</v>
       </c>
       <c r="K259" t="n">
-        <v>5.638437304931245</v>
+        <v>5.695336778554796</v>
       </c>
     </row>
     <row r="260">
@@ -11101,7 +11101,7 @@
         <v>11</v>
       </c>
       <c r="K260" t="n">
-        <v>5.873251756122735</v>
+        <v>5.916398881090648</v>
       </c>
     </row>
     <row r="261">
@@ -11142,7 +11142,7 @@
         <v>11</v>
       </c>
       <c r="K261" t="n">
-        <v>6.018907592463056</v>
+        <v>6.028466787017669</v>
       </c>
     </row>
     <row r="262">
@@ -11183,7 +11183,7 @@
         <v>11</v>
       </c>
       <c r="K262" t="n">
-        <v>6.13033377903689</v>
+        <v>6.183089036257851</v>
       </c>
     </row>
     <row r="263">
@@ -11224,7 +11224,7 @@
         <v>11</v>
       </c>
       <c r="K263" t="n">
-        <v>6.195896005744538</v>
+        <v>6.183089036257851</v>
       </c>
     </row>
     <row r="264">
@@ -11265,7 +11265,7 @@
         <v>11</v>
       </c>
       <c r="K264" t="n">
-        <v>6.693887228585847</v>
+        <v>6.678502812691311</v>
       </c>
     </row>
     <row r="265">
@@ -11306,7 +11306,7 @@
         <v>11</v>
       </c>
       <c r="K265" t="n">
-        <v>6.779875809938758</v>
+        <v>6.762910105951537</v>
       </c>
     </row>
     <row r="266">
@@ -11347,7 +11347,7 @@
         <v>11</v>
       </c>
       <c r="K266" t="n">
-        <v>6.779875809938758</v>
+        <v>6.762910105951537</v>
       </c>
     </row>
     <row r="267">
@@ -11388,7 +11388,7 @@
         <v>11</v>
       </c>
       <c r="K267" t="n">
-        <v>6.951360109820846</v>
+        <v>6.958035336089496</v>
       </c>
     </row>
     <row r="268">
@@ -11429,7 +11429,7 @@
         <v>11</v>
       </c>
       <c r="K268" t="n">
-        <v>7.044519951193478</v>
+        <v>7.038863184843945</v>
       </c>
     </row>
     <row r="269">
@@ -11470,7 +11470,7 @@
         <v>11</v>
       </c>
       <c r="K269" t="n">
-        <v>7.044519951193478</v>
+        <v>7.038863184843945</v>
       </c>
     </row>
     <row r="270">
@@ -11511,7 +11511,7 @@
         <v>11</v>
       </c>
       <c r="K270" t="n">
-        <v>7.053069705022225</v>
+        <v>7.048533837236546</v>
       </c>
     </row>
     <row r="271">
@@ -11552,7 +11552,7 @@
         <v>11</v>
       </c>
       <c r="K271" t="n">
-        <v>7.122511176495668</v>
+        <v>7.120149933515203</v>
       </c>
     </row>
     <row r="272">
@@ -11593,7 +11593,7 @@
         <v>11</v>
       </c>
       <c r="K272" t="n">
-        <v>7.124844508728098</v>
+        <v>7.123924480101738</v>
       </c>
     </row>
     <row r="273">
@@ -11634,7 +11634,7 @@
         <v>11</v>
       </c>
       <c r="K273" t="n">
-        <v>7.115894493709764</v>
+        <v>7.09981303915087</v>
       </c>
     </row>
     <row r="274">
@@ -11675,7 +11675,7 @@
         <v>11</v>
       </c>
       <c r="K274" t="n">
-        <v>7.082376432777282</v>
+        <v>7.088557197797001</v>
       </c>
     </row>
     <row r="275">
@@ -11716,7 +11716,7 @@
         <v>11</v>
       </c>
       <c r="K275" t="n">
-        <v>7.082376432777282</v>
+        <v>7.048245770662089</v>
       </c>
     </row>
     <row r="276">
@@ -11757,7 +11757,7 @@
         <v>11</v>
       </c>
       <c r="K276" t="n">
-        <v>6.967957316948276</v>
+        <v>6.970867491897214</v>
       </c>
     </row>
     <row r="277">
@@ -11798,7 +11798,7 @@
         <v>11</v>
       </c>
       <c r="K277" t="n">
-        <v>6.916648445880319</v>
+        <v>6.916990228205681</v>
       </c>
     </row>
     <row r="278">
@@ -11839,7 +11839,7 @@
         <v>11</v>
       </c>
       <c r="K278" t="n">
-        <v>6.904840842324523</v>
+        <v>6.901385919680333</v>
       </c>
     </row>
     <row r="279">
@@ -11880,7 +11880,7 @@
         <v>11</v>
       </c>
       <c r="K279" t="n">
-        <v>6.897544690717763</v>
+        <v>6.898504876074289</v>
       </c>
     </row>
     <row r="280">
@@ -11921,7 +11921,7 @@
         <v>11</v>
       </c>
       <c r="K280" t="n">
-        <v>6.89676262648014</v>
+        <v>6.897895006967339</v>
       </c>
     </row>
     <row r="281">
@@ -11962,7 +11962,7 @@
         <v>11</v>
       </c>
       <c r="K281" t="n">
-        <v>6.89676262648014</v>
+        <v>6.897895006967339</v>
       </c>
     </row>
     <row r="282">
@@ -12003,7 +12003,7 @@
         <v>11</v>
       </c>
       <c r="K282" t="n">
-        <v>6.89676262648014</v>
+        <v>6.89874950495251</v>
       </c>
     </row>
     <row r="283">
@@ -12044,7 +12044,7 @@
         <v>11</v>
       </c>
       <c r="K283" t="n">
-        <v>6.89676262648014</v>
+        <v>6.89874950495251</v>
       </c>
     </row>
     <row r="284">
@@ -12085,7 +12085,7 @@
         <v>11</v>
       </c>
       <c r="K284" t="n">
-        <v>6.966352942372181</v>
+        <v>6.957842604631645</v>
       </c>
     </row>
     <row r="285">
@@ -12126,7 +12126,7 @@
         <v>11</v>
       </c>
       <c r="K285" t="n">
-        <v>6.966352942372181</v>
+        <v>6.973086915334399</v>
       </c>
     </row>
     <row r="286">
@@ -12167,7 +12167,7 @@
         <v>11</v>
       </c>
       <c r="K286" t="n">
-        <v>7.08329569952153</v>
+        <v>7.089575806623275</v>
       </c>
     </row>
     <row r="287">
@@ -12208,7 +12208,7 @@
         <v>11</v>
       </c>
       <c r="K287" t="n">
-        <v>7.113318836971652</v>
+        <v>7.115566279879215</v>
       </c>
     </row>
     <row r="288">
@@ -12249,7 +12249,7 @@
         <v>11</v>
       </c>
       <c r="K288" t="n">
-        <v>7.081439971448925</v>
+        <v>7.082718528099352</v>
       </c>
     </row>
     <row r="289">
@@ -12290,7 +12290,7 @@
         <v>11</v>
       </c>
       <c r="K289" t="n">
-        <v>7.081439971448925</v>
+        <v>7.082718528099352</v>
       </c>
     </row>
     <row r="290">
@@ -12331,7 +12331,7 @@
         <v>11</v>
       </c>
       <c r="K290" t="n">
-        <v>7.078309026932048</v>
+        <v>7.079942681613507</v>
       </c>
     </row>
     <row r="291">
@@ -12372,7 +12372,7 @@
         <v>11</v>
       </c>
       <c r="K291" t="n">
-        <v>7.063679168615509</v>
+        <v>7.056571411599323</v>
       </c>
     </row>
     <row r="292">
@@ -12413,7 +12413,7 @@
         <v>11</v>
       </c>
       <c r="K292" t="n">
-        <v>7.039427835241649</v>
+        <v>7.041421072292732</v>
       </c>
     </row>
     <row r="293">
@@ -12454,7 +12454,7 @@
         <v>11</v>
       </c>
       <c r="K293" t="n">
-        <v>6.936418497111477</v>
+        <v>6.944025023932241</v>
       </c>
     </row>
     <row r="294">
@@ -12495,7 +12495,7 @@
         <v>11</v>
       </c>
       <c r="K294" t="n">
-        <v>6.922351610295516</v>
+        <v>6.929506203409956</v>
       </c>
     </row>
     <row r="295">
@@ -12536,7 +12536,7 @@
         <v>11</v>
       </c>
       <c r="K295" t="n">
-        <v>6.878724500268678</v>
+        <v>6.887585162000854</v>
       </c>
     </row>
     <row r="296">
@@ -12577,7 +12577,7 @@
         <v>11</v>
       </c>
       <c r="K296" t="n">
-        <v>6.742186433072225</v>
+        <v>6.752761844583099</v>
       </c>
     </row>
     <row r="297">
@@ -12618,7 +12618,7 @@
         <v>11</v>
       </c>
       <c r="K297" t="n">
-        <v>6.609034863503038</v>
+        <v>6.614197956781698</v>
       </c>
     </row>
     <row r="298">
@@ -12659,7 +12659,7 @@
         <v>11</v>
       </c>
       <c r="K298" t="n">
-        <v>6.570646121148647</v>
+        <v>6.575632181637065</v>
       </c>
     </row>
     <row r="299">
@@ -12700,7 +12700,7 @@
         <v>11</v>
       </c>
       <c r="K299" t="n">
-        <v>6.570646121148647</v>
+        <v>6.575632181637065</v>
       </c>
     </row>
     <row r="300">
@@ -12741,7 +12741,7 @@
         <v>11</v>
       </c>
       <c r="K300" t="n">
-        <v>6.535603829282942</v>
+        <v>6.54368727632469</v>
       </c>
     </row>
     <row r="301">
@@ -12782,7 +12782,7 @@
         <v>11</v>
       </c>
       <c r="K301" t="n">
-        <v>6.520739060970818</v>
+        <v>6.481483433844264</v>
       </c>
     </row>
     <row r="302">
@@ -12823,7 +12823,7 @@
         <v>11</v>
       </c>
       <c r="K302" t="n">
-        <v>6.469484996372962</v>
+        <v>6.481483433844264</v>
       </c>
     </row>
     <row r="303">
@@ -12864,7 +12864,7 @@
         <v>11</v>
       </c>
       <c r="K303" t="n">
-        <v>6.469484996372962</v>
+        <v>6.458401017188955</v>
       </c>
     </row>
     <row r="304">
@@ -12905,7 +12905,7 @@
         <v>11</v>
       </c>
       <c r="K304" t="n">
-        <v>6.3578345735016</v>
+        <v>6.370127664668397</v>
       </c>
     </row>
     <row r="305">
@@ -12946,7 +12946,7 @@
         <v>11</v>
       </c>
       <c r="K305" t="n">
-        <v>6.028051041141805</v>
+        <v>6.047094565128257</v>
       </c>
     </row>
     <row r="306">
@@ -12987,7 +12987,7 @@
         <v>11</v>
       </c>
       <c r="K306" t="n">
-        <v>6.028051041141805</v>
+        <v>6.047094565128257</v>
       </c>
     </row>
     <row r="307">
@@ -13028,7 +13028,7 @@
         <v>11</v>
       </c>
       <c r="K307" t="n">
-        <v>5.909486565983412</v>
+        <v>5.934742843658721</v>
       </c>
     </row>
     <row r="308">
@@ -13069,7 +13069,7 @@
         <v>11</v>
       </c>
       <c r="K308" t="n">
-        <v>5.86525818324245</v>
+        <v>5.886282060566358</v>
       </c>
     </row>
     <row r="309">
@@ -13110,7 +13110,7 @@
         <v>11</v>
       </c>
       <c r="K309" t="n">
-        <v>5.748277270865179</v>
+        <v>5.771455990772731</v>
       </c>
     </row>
     <row r="310">
@@ -13151,7 +13151,7 @@
         <v>11</v>
       </c>
       <c r="K310" t="n">
-        <v>5.70911628858416</v>
+        <v>5.628193116648641</v>
       </c>
     </row>
     <row r="311">
@@ -13192,7 +13192,7 @@
         <v>11</v>
       </c>
       <c r="K311" t="n">
-        <v>5.569692532092335</v>
+        <v>5.58740877438313</v>
       </c>
     </row>
     <row r="312">
@@ -13233,7 +13233,7 @@
         <v>11</v>
       </c>
       <c r="K312" t="n">
-        <v>5.427729045060196</v>
+        <v>5.445755776281027</v>
       </c>
     </row>
     <row r="313">
@@ -13274,7 +13274,7 @@
         <v>11</v>
       </c>
       <c r="K313" t="n">
-        <v>5.112119489027608</v>
+        <v>5.118857570068958</v>
       </c>
     </row>
     <row r="314">
@@ -13315,7 +13315,7 @@
         <v>11</v>
       </c>
       <c r="K314" t="n">
-        <v>5.065570738825089</v>
+        <v>5.071270702485146</v>
       </c>
     </row>
     <row r="315">
@@ -13356,7 +13356,7 @@
         <v>11</v>
       </c>
       <c r="K315" t="n">
-        <v>5.060308210649662</v>
+        <v>5.103715803943936</v>
       </c>
     </row>
     <row r="316">
@@ -13397,7 +13397,7 @@
         <v>11</v>
       </c>
       <c r="K316" t="n">
-        <v>5.263983240670941</v>
+        <v>5.257067650967738</v>
       </c>
     </row>
     <row r="317">
@@ -13438,7 +13438,7 @@
         <v>11</v>
       </c>
       <c r="K317" t="n">
-        <v>6.007587089689012</v>
+        <v>5.988173272499822</v>
       </c>
     </row>
     <row r="318">
@@ -13479,7 +13479,7 @@
         <v>11</v>
       </c>
       <c r="K318" t="n">
-        <v>6.007587089689012</v>
+        <v>5.988173272499822</v>
       </c>
     </row>
     <row r="319">
@@ -13520,7 +13520,7 @@
         <v>11</v>
       </c>
       <c r="K319" t="n">
-        <v>6.007587089689012</v>
+        <v>5.988173272499822</v>
       </c>
     </row>
     <row r="320">
@@ -13561,7 +13561,7 @@
         <v>11</v>
       </c>
       <c r="K320" t="n">
-        <v>6.469336271134504</v>
+        <v>6.479253750915263</v>
       </c>
     </row>
     <row r="321">
@@ -13602,7 +13602,7 @@
         <v>11</v>
       </c>
       <c r="K321" t="n">
-        <v>6.469336271134504</v>
+        <v>6.509522324818316</v>
       </c>
     </row>
     <row r="322">
@@ -13643,7 +13643,7 @@
         <v>11</v>
       </c>
       <c r="K322" t="n">
-        <v>6.700906395111375</v>
+        <v>6.705798917266498</v>
       </c>
     </row>
     <row r="323">
@@ -13684,7 +13684,7 @@
         <v>11</v>
       </c>
       <c r="K323" t="n">
-        <v>6.773247592778024</v>
+        <v>6.770685952493457</v>
       </c>
     </row>
     <row r="324">
@@ -13725,7 +13725,7 @@
         <v>11</v>
       </c>
       <c r="K324" t="n">
-        <v>6.95746137163957</v>
+        <v>6.953725242847674</v>
       </c>
     </row>
     <row r="325">
@@ -13766,7 +13766,7 @@
         <v>11</v>
       </c>
       <c r="K325" t="n">
-        <v>6.725486202748479</v>
+        <v>6.737616612741861</v>
       </c>
     </row>
     <row r="326">
@@ -13807,7 +13807,7 @@
         <v>11</v>
       </c>
       <c r="K326" t="n">
-        <v>6.725486202748479</v>
+        <v>6.737616612741861</v>
       </c>
     </row>
     <row r="327">
@@ -13848,7 +13848,7 @@
         <v>11</v>
       </c>
       <c r="K327" t="n">
-        <v>6.725486202748479</v>
+        <v>6.737616612741861</v>
       </c>
     </row>
     <row r="328">
@@ -13889,7 +13889,7 @@
         <v>11</v>
       </c>
       <c r="K328" t="n">
-        <v>6.725486202748479</v>
+        <v>6.737616612741861</v>
       </c>
     </row>
     <row r="329">
@@ -13930,7 +13930,7 @@
         <v>11</v>
       </c>
       <c r="K329" t="n">
-        <v>6.492553137972896</v>
+        <v>6.496223821731629</v>
       </c>
     </row>
     <row r="330">
@@ -13971,7 +13971,7 @@
         <v>11</v>
       </c>
       <c r="K330" t="n">
-        <v>6.492553137972896</v>
+        <v>6.496223821731629</v>
       </c>
     </row>
     <row r="331">
@@ -14012,7 +14012,7 @@
         <v>11</v>
       </c>
       <c r="K331" t="n">
-        <v>6.379464695171034</v>
+        <v>6.386168172167237</v>
       </c>
     </row>
     <row r="332">
@@ -14053,7 +14053,7 @@
         <v>11</v>
       </c>
       <c r="K332" t="n">
-        <v>6.268068461095731</v>
+        <v>6.277012795708539</v>
       </c>
     </row>
     <row r="333">
@@ -14094,7 +14094,7 @@
         <v>11</v>
       </c>
       <c r="K333" t="n">
-        <v>6.268068461095731</v>
+        <v>6.211006209691069</v>
       </c>
     </row>
     <row r="334">
@@ -14135,7 +14135,7 @@
         <v>11</v>
       </c>
       <c r="K334" t="n">
-        <v>6.108187247315048</v>
+        <v>6.11904942060582</v>
       </c>
     </row>
     <row r="335">
@@ -14176,7 +14176,7 @@
         <v>11</v>
       </c>
       <c r="K335" t="n">
-        <v>5.990636830982123</v>
+        <v>5.998747852009257</v>
       </c>
     </row>
     <row r="336">
@@ -14217,7 +14217,7 @@
         <v>11</v>
       </c>
       <c r="K336" t="n">
-        <v>5.990636830982123</v>
+        <v>5.938334688837863</v>
       </c>
     </row>
     <row r="337">
@@ -14258,7 +14258,7 @@
         <v>11</v>
       </c>
       <c r="K337" t="n">
-        <v>5.821615457924278</v>
+        <v>5.82871966169767</v>
       </c>
     </row>
     <row r="338">
@@ -14299,7 +14299,7 @@
         <v>11</v>
       </c>
       <c r="K338" t="n">
-        <v>5.578580583124299</v>
+        <v>5.584442830765994</v>
       </c>
     </row>
     <row r="339">
@@ -14340,7 +14340,7 @@
         <v>11</v>
       </c>
       <c r="K339" t="n">
-        <v>5.565114825495787</v>
+        <v>5.569134413855623</v>
       </c>
     </row>
     <row r="340">
@@ -14381,7 +14381,7 @@
         <v>11</v>
       </c>
       <c r="K340" t="n">
-        <v>5.565114825495787</v>
+        <v>5.538786153724096</v>
       </c>
     </row>
     <row r="341">
@@ -14422,7 +14422,7 @@
         <v>11</v>
       </c>
       <c r="K341" t="n">
-        <v>5.397584106562035</v>
+        <v>5.403416934174485</v>
       </c>
     </row>
     <row r="342">
@@ -14463,7 +14463,7 @@
         <v>11</v>
       </c>
       <c r="K342" t="n">
-        <v>5.397584106562035</v>
+        <v>5.387201129506291</v>
       </c>
     </row>
     <row r="343">
@@ -14504,7 +14504,7 @@
         <v>11</v>
       </c>
       <c r="K343" t="n">
-        <v>5.248318174313285</v>
+        <v>5.250315856279017</v>
       </c>
     </row>
     <row r="344">
@@ -14545,7 +14545,7 @@
         <v>11</v>
       </c>
       <c r="K344" t="n">
-        <v>5.228843147838099</v>
+        <v>5.230415344856231</v>
       </c>
     </row>
     <row r="345">
@@ -14586,7 +14586,7 @@
         <v>11</v>
       </c>
       <c r="K345" t="n">
-        <v>5.217591538910087</v>
+        <v>5.219252952940623</v>
       </c>
     </row>
     <row r="346">
@@ -14627,7 +14627,7 @@
         <v>11</v>
       </c>
       <c r="K346" t="n">
-        <v>5.178817877948433</v>
+        <v>5.181079979862163</v>
       </c>
     </row>
     <row r="347">
@@ -14668,7 +14668,7 @@
         <v>11</v>
       </c>
       <c r="K347" t="n">
-        <v>5.178817877948433</v>
+        <v>5.181079979862163</v>
       </c>
     </row>
     <row r="348">
@@ -14709,7 +14709,7 @@
         <v>11</v>
       </c>
       <c r="K348" t="n">
-        <v>5.103047429233414</v>
+        <v>5.104258065601353</v>
       </c>
     </row>
     <row r="349">
@@ -14750,7 +14750,7 @@
         <v>11</v>
       </c>
       <c r="K349" t="n">
-        <v>5.103047429233414</v>
+        <v>5.104258065601353</v>
       </c>
     </row>
     <row r="350">
@@ -14791,7 +14791,7 @@
         <v>11</v>
       </c>
       <c r="K350" t="n">
-        <v>5.087161811153031</v>
+        <v>5.087979633533983</v>
       </c>
     </row>
     <row r="351">
@@ -14832,7 +14832,7 @@
         <v>11</v>
       </c>
       <c r="K351" t="n">
-        <v>5.066107742005237</v>
+        <v>5.063636724717673</v>
       </c>
     </row>
     <row r="352">
@@ -14873,7 +14873,7 @@
         <v>11</v>
       </c>
       <c r="K352" t="n">
-        <v>5.053594934442158</v>
+        <v>5.054082251193528</v>
       </c>
     </row>
     <row r="353">
@@ -14914,7 +14914,7 @@
         <v>11</v>
       </c>
       <c r="K353" t="n">
-        <v>5.051828699512906</v>
+        <v>5.052025885059392</v>
       </c>
     </row>
     <row r="354">
@@ -14955,7 +14955,7 @@
         <v>11</v>
       </c>
       <c r="K354" t="n">
-        <v>5.051828699512906</v>
+        <v>5.051608165175887</v>
       </c>
     </row>
     <row r="355">
@@ -14996,7 +14996,7 @@
         <v>11</v>
       </c>
       <c r="K355" t="n">
-        <v>5.033611426905216</v>
+        <v>5.03420560269971</v>
       </c>
     </row>
     <row r="356">
@@ -15037,7 +15037,7 @@
         <v>11</v>
       </c>
       <c r="K356" t="n">
-        <v>4.929275832857682</v>
+        <v>4.928011177643681</v>
       </c>
     </row>
     <row r="357">
@@ -15078,7 +15078,7 @@
         <v>11</v>
       </c>
       <c r="K357" t="n">
-        <v>4.929275832857682</v>
+        <v>4.928011177643681</v>
       </c>
     </row>
     <row r="358">
@@ -15119,7 +15119,7 @@
         <v>11</v>
       </c>
       <c r="K358" t="n">
-        <v>4.872454625107524</v>
+        <v>4.874518465457386</v>
       </c>
     </row>
     <row r="359">
@@ -15160,7 +15160,7 @@
         <v>11</v>
       </c>
       <c r="K359" t="n">
-        <v>4.872454625107524</v>
+        <v>4.874518465457386</v>
       </c>
     </row>
     <row r="360">
@@ -15201,7 +15201,7 @@
         <v>11</v>
       </c>
       <c r="K360" t="n">
-        <v>4.872454625107524</v>
+        <v>4.874518465457386</v>
       </c>
     </row>
     <row r="361">
@@ -15242,7 +15242,7 @@
         <v>11</v>
       </c>
       <c r="K361" t="n">
-        <v>4.623009871540489</v>
+        <v>4.597762906243404</v>
       </c>
     </row>
     <row r="362">
@@ -15283,7 +15283,7 @@
         <v>11</v>
       </c>
       <c r="K362" t="n">
-        <v>4.456714891840787</v>
+        <v>4.462834222282599</v>
       </c>
     </row>
     <row r="363">
@@ -15324,7 +15324,7 @@
         <v>11</v>
       </c>
       <c r="K363" t="n">
-        <v>4.239164569907135</v>
+        <v>4.240451285547139</v>
       </c>
     </row>
     <row r="364">
@@ -15365,7 +15365,7 @@
         <v>11</v>
       </c>
       <c r="K364" t="n">
-        <v>4.229815556186312</v>
+        <v>4.229544701497171</v>
       </c>
     </row>
     <row r="365">
@@ -15406,7 +15406,7 @@
         <v>11</v>
       </c>
       <c r="K365" t="n">
-        <v>4.264805048220962</v>
+        <v>4.257893307290076</v>
       </c>
     </row>
     <row r="366">
@@ -15447,7 +15447,7 @@
         <v>11</v>
       </c>
       <c r="K366" t="n">
-        <v>4.640482551379715</v>
+        <v>4.731254471357712</v>
       </c>
     </row>
     <row r="367">
@@ -15488,7 +15488,7 @@
         <v>13</v>
       </c>
       <c r="K367" t="n">
-        <v>4.989004572852498</v>
+        <v>5.009051159977791</v>
       </c>
     </row>
     <row r="368">
@@ -15529,7 +15529,7 @@
         <v>13</v>
       </c>
       <c r="K368" t="n">
-        <v>4.989004572852498</v>
+        <v>5.009051159977791</v>
       </c>
     </row>
     <row r="369">
@@ -15570,7 +15570,7 @@
         <v>13</v>
       </c>
       <c r="K369" t="n">
-        <v>5.146464818680906</v>
+        <v>5.15880647609656</v>
       </c>
     </row>
     <row r="370">
@@ -15611,7 +15611,7 @@
         <v>13</v>
       </c>
       <c r="K370" t="n">
-        <v>5.353125367080958</v>
+        <v>5.355917306458863</v>
       </c>
     </row>
     <row r="371">
@@ -15652,7 +15652,7 @@
         <v>13</v>
       </c>
       <c r="K371" t="n">
-        <v>5.353125367080958</v>
+        <v>5.355917306458863</v>
       </c>
     </row>
     <row r="372">
@@ -15693,7 +15693,7 @@
         <v>13</v>
       </c>
       <c r="K372" t="n">
-        <v>4.779058792993079</v>
+        <v>4.831510939210975</v>
       </c>
     </row>
     <row r="373">
@@ -15734,7 +15734,7 @@
         <v>13</v>
       </c>
       <c r="K373" t="n">
-        <v>4.553460460182328</v>
+        <v>4.58396786830279</v>
       </c>
     </row>
     <row r="374">
@@ -15775,7 +15775,7 @@
         <v>13</v>
       </c>
       <c r="K374" t="n">
-        <v>4.511632037825243</v>
+        <v>4.528597978191947</v>
       </c>
     </row>
     <row r="375">
@@ -15816,7 +15816,7 @@
         <v>13</v>
       </c>
       <c r="K375" t="n">
-        <v>4.409510797659138</v>
+        <v>4.416973149188368</v>
       </c>
     </row>
     <row r="376">
@@ -15857,7 +15857,7 @@
         <v>13</v>
       </c>
       <c r="K376" t="n">
-        <v>4.371913944205286</v>
+        <v>4.376289310877026</v>
       </c>
     </row>
     <row r="377">
@@ -15898,7 +15898,7 @@
         <v>13</v>
       </c>
       <c r="K377" t="n">
-        <v>4.362506847215201</v>
+        <v>4.364069353716594</v>
       </c>
     </row>
     <row r="378">
@@ -15939,7 +15939,7 @@
         <v>13</v>
       </c>
       <c r="K378" t="n">
-        <v>4.359802946206667</v>
+        <v>4.359392543713576</v>
       </c>
     </row>
     <row r="379">
@@ -15980,7 +15980,7 @@
         <v>13</v>
       </c>
       <c r="K379" t="n">
-        <v>4.398441205772128</v>
+        <v>4.396368908958507</v>
       </c>
     </row>
     <row r="380">
@@ -16021,7 +16021,7 @@
         <v>13</v>
       </c>
       <c r="K380" t="n">
-        <v>4.60277155534549</v>
+        <v>4.600737642609507</v>
       </c>
     </row>
     <row r="381">
@@ -16062,7 +16062,7 @@
         <v>13</v>
       </c>
       <c r="K381" t="n">
-        <v>4.643986846759577</v>
+        <v>4.639414539482974</v>
       </c>
     </row>
     <row r="382">
@@ -16103,7 +16103,7 @@
         <v>13</v>
       </c>
       <c r="K382" t="n">
-        <v>4.848354479857987</v>
+        <v>4.859919451808512</v>
       </c>
     </row>
     <row r="383">
@@ -16144,7 +16144,7 @@
         <v>13</v>
       </c>
       <c r="K383" t="n">
-        <v>4.87352437788092</v>
+        <v>4.877145691804395</v>
       </c>
     </row>
     <row r="384">
@@ -16185,7 +16185,7 @@
         <v>13</v>
       </c>
       <c r="K384" t="n">
-        <v>4.899747783476667</v>
+        <v>4.899401674546827</v>
       </c>
     </row>
     <row r="385">
@@ -16226,7 +16226,7 @@
         <v>13</v>
       </c>
       <c r="K385" t="n">
-        <v>4.907146729781727</v>
+        <v>4.907586573854535</v>
       </c>
     </row>
     <row r="386">
@@ -16267,7 +16267,7 @@
         <v>13</v>
       </c>
       <c r="K386" t="n">
-        <v>4.877304192149911</v>
+        <v>4.877377400066405</v>
       </c>
     </row>
     <row r="387">
@@ -16308,7 +16308,7 @@
         <v>13</v>
       </c>
       <c r="K387" t="n">
-        <v>4.887105425513584</v>
+        <v>4.886258008494034</v>
       </c>
     </row>
     <row r="388">
@@ -16349,7 +16349,7 @@
         <v>13</v>
       </c>
       <c r="K388" t="n">
-        <v>4.891508207700674</v>
+        <v>4.890975316997407</v>
       </c>
     </row>
     <row r="389">
@@ -16390,7 +16390,7 @@
         <v>13</v>
       </c>
       <c r="K389" t="n">
-        <v>4.944967934531709</v>
+        <v>4.943995443063672</v>
       </c>
     </row>
     <row r="390">
@@ -16431,7 +16431,7 @@
         <v>13</v>
       </c>
       <c r="K390" t="n">
-        <v>4.944967934531709</v>
+        <v>4.943995443063672</v>
       </c>
     </row>
     <row r="391">
@@ -16472,7 +16472,7 @@
         <v>13</v>
       </c>
       <c r="K391" t="n">
-        <v>4.941879321124623</v>
+        <v>4.944986251029172</v>
       </c>
     </row>
     <row r="392">
@@ -16513,7 +16513,7 @@
         <v>13</v>
       </c>
       <c r="K392" t="n">
-        <v>4.860825523074782</v>
+        <v>4.863151805751876</v>
       </c>
     </row>
     <row r="393">
@@ -16554,7 +16554,7 @@
         <v>13</v>
       </c>
       <c r="K393" t="n">
-        <v>4.816185372030051</v>
+        <v>4.820800367261343</v>
       </c>
     </row>
     <row r="394">
@@ -16595,7 +16595,7 @@
         <v>13</v>
       </c>
       <c r="K394" t="n">
-        <v>4.792663898081057</v>
+        <v>4.795040460349449</v>
       </c>
     </row>
     <row r="395">
@@ -16636,7 +16636,7 @@
         <v>13</v>
       </c>
       <c r="K395" t="n">
-        <v>4.603755169870238</v>
+        <v>4.577499416625013</v>
       </c>
     </row>
     <row r="396">
@@ -16677,7 +16677,7 @@
         <v>13</v>
       </c>
       <c r="K396" t="n">
-        <v>4.574525663067135</v>
+        <v>4.52733212876464</v>
       </c>
     </row>
     <row r="397">
@@ -16718,7 +16718,7 @@
         <v>13</v>
       </c>
       <c r="K397" t="n">
-        <v>4.522152660552515</v>
+        <v>4.52733212876464</v>
       </c>
     </row>
     <row r="398">
@@ -16759,7 +16759,7 @@
         <v>13</v>
       </c>
       <c r="K398" t="n">
-        <v>4.447062046522253</v>
+        <v>4.451729462147042</v>
       </c>
     </row>
     <row r="399">
@@ -16800,7 +16800,7 @@
         <v>13</v>
       </c>
       <c r="K399" t="n">
-        <v>4.424926843689395</v>
+        <v>4.427051227433752</v>
       </c>
     </row>
     <row r="400">
@@ -16841,7 +16841,7 @@
         <v>13</v>
       </c>
       <c r="K400" t="n">
-        <v>4.281796757974083</v>
+        <v>4.283055356823215</v>
       </c>
     </row>
     <row r="401">
@@ -16882,7 +16882,7 @@
         <v>13</v>
       </c>
       <c r="K401" t="n">
-        <v>4.281796757974083</v>
+        <v>4.283055356823215</v>
       </c>
     </row>
     <row r="402">
@@ -16923,7 +16923,7 @@
         <v>13</v>
       </c>
       <c r="K402" t="n">
-        <v>4.251537092101995</v>
+        <v>4.252142257147563</v>
       </c>
     </row>
     <row r="403">
@@ -16964,7 +16964,7 @@
         <v>13</v>
       </c>
       <c r="K403" t="n">
-        <v>4.251537092101995</v>
+        <v>4.252142257147563</v>
       </c>
     </row>
     <row r="404">
@@ -17005,7 +17005,7 @@
         <v>13</v>
       </c>
       <c r="K404" t="n">
-        <v>4.292707926907702</v>
+        <v>4.290690832725846</v>
       </c>
     </row>
     <row r="405">
@@ -17046,7 +17046,7 @@
         <v>13</v>
       </c>
       <c r="K405" t="n">
-        <v>4.334245158058574</v>
+        <v>4.333123603095071</v>
       </c>
     </row>
     <row r="406">
@@ -17087,7 +17087,7 @@
         <v>13</v>
       </c>
       <c r="K406" t="n">
-        <v>4.334245158058574</v>
+        <v>4.333123603095071</v>
       </c>
     </row>
     <row r="407">
@@ -17128,7 +17128,7 @@
         <v>13</v>
       </c>
       <c r="K407" t="n">
-        <v>4.447275998440267</v>
+        <v>4.446015187643931</v>
       </c>
     </row>
     <row r="408">
@@ -17169,7 +17169,7 @@
         <v>13</v>
       </c>
       <c r="K408" t="n">
-        <v>4.511652799781686</v>
+        <v>4.510663146583182</v>
       </c>
     </row>
     <row r="409">
@@ -17210,7 +17210,7 @@
         <v>13</v>
       </c>
       <c r="K409" t="n">
-        <v>4.557602765704349</v>
+        <v>4.555957380697734</v>
       </c>
     </row>
     <row r="410">
@@ -17251,7 +17251,7 @@
         <v>13</v>
       </c>
       <c r="K410" t="n">
-        <v>4.557602765704349</v>
+        <v>4.555957380697734</v>
       </c>
     </row>
     <row r="411">
@@ -17292,7 +17292,7 @@
         <v>13</v>
       </c>
       <c r="K411" t="n">
-        <v>4.592489498071687</v>
+        <v>4.592699341187079</v>
       </c>
     </row>
     <row r="412">
@@ -17333,7 +17333,7 @@
         <v>13</v>
       </c>
       <c r="K412" t="n">
-        <v>4.587032584585324</v>
+        <v>4.587486027980054</v>
       </c>
     </row>
     <row r="413">
@@ -17374,7 +17374,7 @@
         <v>13</v>
       </c>
       <c r="K413" t="n">
-        <v>4.585284292425333</v>
+        <v>4.584321202587487</v>
       </c>
     </row>
     <row r="414">
@@ -17415,7 +17415,7 @@
         <v>13</v>
       </c>
       <c r="K414" t="n">
-        <v>4.589465066943817</v>
+        <v>4.58890998344388</v>
       </c>
     </row>
     <row r="415">
@@ -17456,7 +17456,7 @@
         <v>13</v>
       </c>
       <c r="K415" t="n">
-        <v>4.592689708661526</v>
+        <v>4.592351708632568</v>
       </c>
     </row>
     <row r="416">
@@ -17497,7 +17497,7 @@
         <v>13</v>
       </c>
       <c r="K416" t="n">
-        <v>4.597686465100862</v>
+        <v>4.594883883067804</v>
       </c>
     </row>
     <row r="417">
@@ -17538,7 +17538,7 @@
         <v>13</v>
       </c>
       <c r="K417" t="n">
-        <v>4.569534921982572</v>
+        <v>4.570479752993418</v>
       </c>
     </row>
     <row r="418">
@@ -17579,7 +17579,7 @@
         <v>13</v>
       </c>
       <c r="K418" t="n">
-        <v>4.540415429587346</v>
+        <v>4.541277659364386</v>
       </c>
     </row>
     <row r="419">
@@ -17620,7 +17620,7 @@
         <v>13</v>
       </c>
       <c r="K419" t="n">
-        <v>4.540415429587346</v>
+        <v>4.541277659364386</v>
       </c>
     </row>
     <row r="420">
@@ -17661,7 +17661,7 @@
         <v>13</v>
       </c>
       <c r="K420" t="n">
-        <v>4.510857780145722</v>
+        <v>4.511235419460088</v>
       </c>
     </row>
     <row r="421">
@@ -17702,7 +17702,7 @@
         <v>13</v>
       </c>
       <c r="K421" t="n">
-        <v>4.490591228908446</v>
+        <v>4.491951816673529</v>
       </c>
     </row>
     <row r="422">
@@ -17743,7 +17743,7 @@
         <v>13</v>
       </c>
       <c r="K422" t="n">
-        <v>4.45464842483792</v>
+        <v>4.45625348000839</v>
       </c>
     </row>
     <row r="423">
@@ -17784,7 +17784,7 @@
         <v>13</v>
       </c>
       <c r="K423" t="n">
-        <v>4.45464842483792</v>
+        <v>4.45625348000839</v>
       </c>
     </row>
     <row r="424">
@@ -17825,7 +17825,7 @@
         <v>13</v>
       </c>
       <c r="K424" t="n">
-        <v>4.394913341802887</v>
+        <v>4.396204559299213</v>
       </c>
     </row>
     <row r="425">
@@ -17866,7 +17866,7 @@
         <v>13</v>
       </c>
       <c r="K425" t="n">
-        <v>4.394913341802887</v>
+        <v>4.396204559299213</v>
       </c>
     </row>
     <row r="426">
@@ -17907,7 +17907,7 @@
         <v>13</v>
       </c>
       <c r="K426" t="n">
-        <v>4.364755589609413</v>
+        <v>4.36800815740139</v>
       </c>
     </row>
     <row r="427">
@@ -17948,7 +17948,7 @@
         <v>13</v>
       </c>
       <c r="K427" t="n">
-        <v>4.240943436944539</v>
+        <v>4.242718408837438</v>
       </c>
     </row>
     <row r="428">
@@ -17989,7 +17989,7 @@
         <v>13</v>
       </c>
       <c r="K428" t="n">
-        <v>4.198404585277019</v>
+        <v>4.200254345989413</v>
       </c>
     </row>
     <row r="429">
@@ -18030,7 +18030,7 @@
         <v>13</v>
       </c>
       <c r="K429" t="n">
-        <v>4.181644802872792</v>
+        <v>4.151373321822546</v>
       </c>
     </row>
     <row r="430">
@@ -18071,7 +18071,7 @@
         <v>13</v>
       </c>
       <c r="K430" t="n">
-        <v>4.181644802872792</v>
+        <v>4.151373321822546</v>
       </c>
     </row>
     <row r="431">
@@ -18112,7 +18112,7 @@
         <v>13</v>
       </c>
       <c r="K431" t="n">
-        <v>4.147642734804</v>
+        <v>4.151373321822546</v>
       </c>
     </row>
     <row r="432">
@@ -18153,7 +18153,7 @@
         <v>13</v>
       </c>
       <c r="K432" t="n">
-        <v>4.147642734804</v>
+        <v>4.151373321822546</v>
       </c>
     </row>
     <row r="433">
@@ -18194,7 +18194,7 @@
         <v>13</v>
       </c>
       <c r="K433" t="n">
-        <v>3.991336485802085</v>
+        <v>3.994694624172563</v>
       </c>
     </row>
     <row r="434">
@@ -18235,7 +18235,7 @@
         <v>13</v>
       </c>
       <c r="K434" t="n">
-        <v>3.969907461821541</v>
+        <v>3.97115691102894</v>
       </c>
     </row>
     <row r="435">
@@ -18276,7 +18276,7 @@
         <v>13</v>
       </c>
       <c r="K435" t="n">
-        <v>3.671254998183573</v>
+        <v>3.67548319623551</v>
       </c>
     </row>
     <row r="436">
@@ -18317,7 +18317,7 @@
         <v>13</v>
       </c>
       <c r="K436" t="n">
-        <v>3.534008439782921</v>
+        <v>3.537527711760136</v>
       </c>
     </row>
     <row r="437">
@@ -18358,7 +18358,7 @@
         <v>13</v>
       </c>
       <c r="K437" t="n">
-        <v>3.233298133780483</v>
+        <v>3.234246051241239</v>
       </c>
     </row>
     <row r="438">
@@ -18399,7 +18399,7 @@
         <v>13</v>
       </c>
       <c r="K438" t="n">
-        <v>3.212345670607433</v>
+        <v>3.214625926265903</v>
       </c>
     </row>
     <row r="439">
@@ -18440,7 +18440,7 @@
         <v>13</v>
       </c>
       <c r="K439" t="n">
-        <v>3.146542260900836</v>
+        <v>3.147124019384793</v>
       </c>
     </row>
     <row r="440">
@@ -18481,7 +18481,7 @@
         <v>13</v>
       </c>
       <c r="K440" t="n">
-        <v>3.146542260900836</v>
+        <v>3.147124019384793</v>
       </c>
     </row>
     <row r="441">
@@ -18522,7 +18522,7 @@
         <v>13</v>
       </c>
       <c r="K441" t="n">
-        <v>2.94136201973682</v>
+        <v>2.946375462561702</v>
       </c>
     </row>
     <row r="442">
@@ -18563,7 +18563,7 @@
         <v>13</v>
       </c>
       <c r="K442" t="n">
-        <v>2.913163314422679</v>
+        <v>2.915349648297191</v>
       </c>
     </row>
     <row r="443">
@@ -18604,7 +18604,7 @@
         <v>13</v>
       </c>
       <c r="K443" t="n">
-        <v>2.867826113041806</v>
+        <v>2.872435751907907</v>
       </c>
     </row>
     <row r="444">
@@ -18645,7 +18645,7 @@
         <v>13</v>
       </c>
       <c r="K444" t="n">
-        <v>2.867826113041806</v>
+        <v>2.872435751907907</v>
       </c>
     </row>
     <row r="445">
@@ -18686,7 +18686,7 @@
         <v>13</v>
       </c>
       <c r="K445" t="n">
-        <v>2.747673157304389</v>
+        <v>2.75060963752063</v>
       </c>
     </row>
     <row r="446">
@@ -18727,7 +18727,7 @@
         <v>13</v>
       </c>
       <c r="K446" t="n">
-        <v>2.648465739207162</v>
+        <v>2.651966855346455</v>
       </c>
     </row>
     <row r="447">
@@ -18768,7 +18768,7 @@
         <v>13</v>
       </c>
       <c r="K447" t="n">
-        <v>2.628198666461623</v>
+        <v>2.629794555295281</v>
       </c>
     </row>
     <row r="448">
@@ -18809,7 +18809,7 @@
         <v>13</v>
       </c>
       <c r="K448" t="n">
-        <v>2.575768250708054</v>
+        <v>2.57713737578871</v>
       </c>
     </row>
     <row r="449">
@@ -18850,7 +18850,7 @@
         <v>13</v>
       </c>
       <c r="K449" t="n">
-        <v>2.549580793148484</v>
+        <v>2.551989569946513</v>
       </c>
     </row>
     <row r="450">
@@ -18891,7 +18891,7 @@
         <v>13</v>
       </c>
       <c r="K450" t="n">
-        <v>2.523018486360694</v>
+        <v>2.524061377829816</v>
       </c>
     </row>
     <row r="451">
@@ -18932,7 +18932,7 @@
         <v>13</v>
       </c>
       <c r="K451" t="n">
-        <v>2.525904809614844</v>
+        <v>2.525082793003739</v>
       </c>
     </row>
     <row r="452">
@@ -18973,7 +18973,7 @@
         <v>13</v>
       </c>
       <c r="K452" t="n">
-        <v>2.530763611856992</v>
+        <v>2.530421442454421</v>
       </c>
     </row>
     <row r="453">
@@ -19014,7 +19014,7 @@
         <v>13</v>
       </c>
       <c r="K453" t="n">
-        <v>2.538924708444407</v>
+        <v>2.538106187610786</v>
       </c>
     </row>
     <row r="454">
@@ -19055,7 +19055,7 @@
         <v>13</v>
       </c>
       <c r="K454" t="n">
-        <v>2.551977826887383</v>
+        <v>2.551097632605253</v>
       </c>
     </row>
     <row r="455">
@@ -19096,7 +19096,7 @@
         <v>13</v>
       </c>
       <c r="K455" t="n">
-        <v>2.557501097330654</v>
+        <v>2.557053170342221</v>
       </c>
     </row>
     <row r="456">
@@ -19137,7 +19137,7 @@
         <v>13</v>
       </c>
       <c r="K456" t="n">
-        <v>2.568759827354336</v>
+        <v>2.567441500441185</v>
       </c>
     </row>
     <row r="457">
@@ -19178,7 +19178,7 @@
         <v>13</v>
       </c>
       <c r="K457" t="n">
-        <v>2.726836335445439</v>
+        <v>2.72387236358276</v>
       </c>
     </row>
     <row r="458">
@@ -19219,7 +19219,7 @@
         <v>13</v>
       </c>
       <c r="K458" t="n">
-        <v>2.796250047711122</v>
+        <v>2.794919995676238</v>
       </c>
     </row>
     <row r="459">
@@ -19260,7 +19260,7 @@
         <v>13</v>
       </c>
       <c r="K459" t="n">
-        <v>2.833016366409367</v>
+        <v>2.832202962519289</v>
       </c>
     </row>
     <row r="460">
@@ -19301,7 +19301,7 @@
         <v>13</v>
       </c>
       <c r="K460" t="n">
-        <v>2.851039590450572</v>
+        <v>2.8512567008004</v>
       </c>
     </row>
     <row r="461">
@@ -19342,7 +19342,7 @@
         <v>13</v>
       </c>
       <c r="K461" t="n">
-        <v>2.850290311605115</v>
+        <v>2.850380399105674</v>
       </c>
     </row>
     <row r="462">
@@ -19383,7 +19383,7 @@
         <v>13</v>
       </c>
       <c r="K462" t="n">
-        <v>2.848985740418553</v>
+        <v>2.849129860246591</v>
       </c>
     </row>
     <row r="463">
@@ -19424,7 +19424,7 @@
         <v>13</v>
       </c>
       <c r="K463" t="n">
-        <v>2.84359152746801</v>
+        <v>2.844125612919445</v>
       </c>
     </row>
     <row r="464">
@@ -19465,7 +19465,7 @@
         <v>13</v>
       </c>
       <c r="K464" t="n">
-        <v>2.83954340835155</v>
+        <v>2.839877714565478</v>
       </c>
     </row>
     <row r="465">
@@ -19506,7 +19506,7 @@
         <v>13</v>
       </c>
       <c r="K465" t="n">
-        <v>2.826395175950948</v>
+        <v>2.826706622385811</v>
       </c>
     </row>
     <row r="466">
@@ -19547,7 +19547,7 @@
         <v>13</v>
       </c>
       <c r="K466" t="n">
-        <v>2.837916938046403</v>
+        <v>2.83774040535544</v>
       </c>
     </row>
     <row r="467">
@@ -19588,7 +19588,7 @@
         <v>13</v>
       </c>
       <c r="K467" t="n">
-        <v>2.837916938046403</v>
+        <v>2.83774040535544</v>
       </c>
     </row>
     <row r="468">
@@ -19629,7 +19629,7 @@
         <v>13</v>
       </c>
       <c r="K468" t="n">
-        <v>2.846359518718809</v>
+        <v>2.846211113453743</v>
       </c>
     </row>
     <row r="469">
@@ -19670,7 +19670,7 @@
         <v>13</v>
       </c>
       <c r="K469" t="n">
-        <v>2.84962665228868</v>
+        <v>2.849555993068426</v>
       </c>
     </row>
     <row r="470">
@@ -19711,7 +19711,7 @@
         <v>13</v>
       </c>
       <c r="K470" t="n">
-        <v>2.851999248513181</v>
+        <v>2.852688989368364</v>
       </c>
     </row>
     <row r="471">
@@ -19752,7 +19752,7 @@
         <v>13</v>
       </c>
       <c r="K471" t="n">
-        <v>2.826791792572971</v>
+        <v>2.82737242464083</v>
       </c>
     </row>
     <row r="472">
@@ -19793,7 +19793,7 @@
         <v>13</v>
       </c>
       <c r="K472" t="n">
-        <v>2.785307233039441</v>
+        <v>2.773113249976281</v>
       </c>
     </row>
     <row r="473">
@@ -19834,7 +19834,7 @@
         <v>13</v>
       </c>
       <c r="K473" t="n">
-        <v>2.684265664996164</v>
+        <v>2.684597503209302</v>
       </c>
     </row>
     <row r="474">
@@ -19875,7 +19875,7 @@
         <v>13</v>
       </c>
       <c r="K474" t="n">
-        <v>2.684265664996164</v>
+        <v>2.684597503209302</v>
       </c>
     </row>
     <row r="475">
@@ -19916,7 +19916,7 @@
         <v>13</v>
       </c>
       <c r="K475" t="n">
-        <v>2.660336897045805</v>
+        <v>2.662193937382735</v>
       </c>
     </row>
     <row r="476">
@@ -19957,7 +19957,7 @@
         <v>13</v>
       </c>
       <c r="K476" t="n">
-        <v>2.625088197187994</v>
+        <v>2.626946957376029</v>
       </c>
     </row>
     <row r="477">
@@ -19998,7 +19998,7 @@
         <v>13</v>
       </c>
       <c r="K477" t="n">
-        <v>2.625088197187994</v>
+        <v>2.626946957376029</v>
       </c>
     </row>
     <row r="478">
@@ -20039,7 +20039,7 @@
         <v>13</v>
       </c>
       <c r="K478" t="n">
-        <v>2.595172871096828</v>
+        <v>2.596561647476353</v>
       </c>
     </row>
     <row r="479">
@@ -20080,7 +20080,7 @@
         <v>13</v>
       </c>
       <c r="K479" t="n">
-        <v>2.557288520504256</v>
+        <v>2.557094794064693</v>
       </c>
     </row>
     <row r="480">
@@ -20121,7 +20121,7 @@
         <v>13</v>
       </c>
       <c r="K480" t="n">
-        <v>2.54723572550443</v>
+        <v>2.546663679800613</v>
       </c>
     </row>
     <row r="481">
@@ -20162,7 +20162,7 @@
         <v>13</v>
       </c>
       <c r="K481" t="n">
-        <v>2.561146256204195</v>
+        <v>2.560653245463377</v>
       </c>
     </row>
     <row r="482">
@@ -20203,7 +20203,7 @@
         <v>13</v>
       </c>
       <c r="K482" t="n">
-        <v>2.577164999305285</v>
+        <v>2.576681123282161</v>
       </c>
     </row>
     <row r="483">
@@ -20244,7 +20244,7 @@
         <v>13</v>
       </c>
       <c r="K483" t="n">
-        <v>2.628999808646188</v>
+        <v>2.628175057573757</v>
       </c>
     </row>
     <row r="484">
@@ -20285,7 +20285,7 @@
         <v>13</v>
       </c>
       <c r="K484" t="n">
-        <v>2.671677257243824</v>
+        <v>2.670642386120931</v>
       </c>
     </row>
     <row r="485">
@@ -20326,7 +20326,7 @@
         <v>13</v>
       </c>
       <c r="K485" t="n">
-        <v>2.822822004619789</v>
+        <v>2.820931860519237</v>
       </c>
     </row>
     <row r="486">
@@ -20367,7 +20367,7 @@
         <v>13</v>
       </c>
       <c r="K486" t="n">
-        <v>2.865774151657083</v>
+        <v>2.865023426732595</v>
       </c>
     </row>
     <row r="487">
@@ -20408,7 +20408,7 @@
         <v>13</v>
       </c>
       <c r="K487" t="n">
-        <v>2.915214548477925</v>
+        <v>2.92888126878154</v>
       </c>
     </row>
     <row r="488">
@@ -20449,7 +20449,7 @@
         <v>13</v>
       </c>
       <c r="K488" t="n">
-        <v>2.99329437495177</v>
+        <v>2.993548354148347</v>
       </c>
     </row>
     <row r="489">
@@ -20490,7 +20490,7 @@
         <v>13</v>
       </c>
       <c r="K489" t="n">
-        <v>2.99329437495177</v>
+        <v>2.993548354148347</v>
       </c>
     </row>
     <row r="490">
@@ -20531,7 +20531,7 @@
         <v>13</v>
       </c>
       <c r="K490" t="n">
-        <v>3.181715602514981</v>
+        <v>3.17743835768284</v>
       </c>
     </row>
     <row r="491">
@@ -20572,7 +20572,7 @@
         <v>13</v>
       </c>
       <c r="K491" t="n">
-        <v>3.181715602514981</v>
+        <v>3.17743835768284</v>
       </c>
     </row>
     <row r="492">
@@ -20613,7 +20613,7 @@
         <v>13</v>
       </c>
       <c r="K492" t="n">
-        <v>3.181715602514981</v>
+        <v>3.17743835768284</v>
       </c>
     </row>
     <row r="493">
@@ -20654,7 +20654,7 @@
         <v>13</v>
       </c>
       <c r="K493" t="n">
-        <v>3.2770992182409</v>
+        <v>3.273688615001583</v>
       </c>
     </row>
     <row r="494">
@@ -20695,7 +20695,7 @@
         <v>13</v>
       </c>
       <c r="K494" t="n">
-        <v>3.401101223750155</v>
+        <v>3.399288115903612</v>
       </c>
     </row>
     <row r="495">
@@ -20736,7 +20736,7 @@
         <v>13</v>
       </c>
       <c r="K495" t="n">
-        <v>3.459700348443766</v>
+        <v>3.458782502549476</v>
       </c>
     </row>
     <row r="496">
@@ -20777,7 +20777,7 @@
         <v>13</v>
       </c>
       <c r="K496" t="n">
-        <v>3.459700348443766</v>
+        <v>3.458782502549476</v>
       </c>
     </row>
     <row r="497">
@@ -20818,7 +20818,7 @@
         <v>13</v>
       </c>
       <c r="K497" t="n">
-        <v>3.519061479695633</v>
+        <v>3.517193804808829</v>
       </c>
     </row>
     <row r="498">
@@ -20859,7 +20859,7 @@
         <v>13</v>
       </c>
       <c r="K498" t="n">
-        <v>3.519061479695633</v>
+        <v>3.532119907048373</v>
       </c>
     </row>
     <row r="499">
@@ -20900,7 +20900,7 @@
         <v>13</v>
       </c>
       <c r="K499" t="n">
-        <v>3.577851334197729</v>
+        <v>3.57644669032979</v>
       </c>
     </row>
     <row r="500">
@@ -20941,7 +20941,7 @@
         <v>13</v>
       </c>
       <c r="K500" t="n">
-        <v>3.609708896446134</v>
+        <v>3.609430363377689</v>
       </c>
     </row>
     <row r="501">
@@ -20982,7 +20982,7 @@
         <v>13</v>
       </c>
       <c r="K501" t="n">
-        <v>3.636170417022504</v>
+        <v>3.635208912104673</v>
       </c>
     </row>
     <row r="502">
@@ -21023,7 +21023,7 @@
         <v>13</v>
       </c>
       <c r="K502" t="n">
-        <v>3.579045313630146</v>
+        <v>3.579582514419914</v>
       </c>
     </row>
     <row r="503">
@@ -21064,7 +21064,7 @@
         <v>13</v>
       </c>
       <c r="K503" t="n">
-        <v>3.508732511688802</v>
+        <v>3.509296183656049</v>
       </c>
     </row>
     <row r="504">
@@ -21105,7 +21105,7 @@
         <v>13</v>
       </c>
       <c r="K504" t="n">
-        <v>3.35340877625111</v>
+        <v>3.356335192423844</v>
       </c>
     </row>
     <row r="505">
@@ -21146,7 +21146,7 @@
         <v>13</v>
       </c>
       <c r="K505" t="n">
-        <v>3.278791341588974</v>
+        <v>3.279530927100807</v>
       </c>
     </row>
     <row r="506">
@@ -21187,7 +21187,7 @@
         <v>13</v>
       </c>
       <c r="K506" t="n">
-        <v>3.234855469215185</v>
+        <v>3.235404949567815</v>
       </c>
     </row>
     <row r="507">
@@ -21228,7 +21228,7 @@
         <v>13</v>
       </c>
       <c r="K507" t="n">
-        <v>3.197646767046158</v>
+        <v>3.198163637987276</v>
       </c>
     </row>
     <row r="508">
@@ -21269,7 +21269,7 @@
         <v>13</v>
       </c>
       <c r="K508" t="n">
-        <v>3.114005783106445</v>
+        <v>3.113982428218768</v>
       </c>
     </row>
     <row r="509">
@@ -21310,7 +21310,7 @@
         <v>13</v>
       </c>
       <c r="K509" t="n">
-        <v>3.11426097831023</v>
+        <v>3.114212846711584</v>
       </c>
     </row>
     <row r="510">
@@ -21351,7 +21351,7 @@
         <v>13</v>
       </c>
       <c r="K510" t="n">
-        <v>3.112285912835071</v>
+        <v>3.112438313982864</v>
       </c>
     </row>
     <row r="511">
@@ -21392,7 +21392,7 @@
         <v>13</v>
       </c>
       <c r="K511" t="n">
-        <v>3.104332796397895</v>
+        <v>3.104966345884675</v>
       </c>
     </row>
     <row r="512">
@@ -21433,7 +21433,7 @@
         <v>13</v>
       </c>
       <c r="K512" t="n">
-        <v>3.089695567119747</v>
+        <v>3.090742098688409</v>
       </c>
     </row>
     <row r="513">
@@ -21474,7 +21474,7 @@
         <v>13</v>
       </c>
       <c r="K513" t="n">
-        <v>3.01865909708095</v>
+        <v>3.019070948120782</v>
       </c>
     </row>
     <row r="514">
@@ -21515,7 +21515,7 @@
         <v>13</v>
       </c>
       <c r="K514" t="n">
-        <v>3.000123538674034</v>
+        <v>3.001976565304254</v>
       </c>
     </row>
     <row r="515">
@@ -21556,7 +21556,7 @@
         <v>13</v>
       </c>
       <c r="K515" t="n">
-        <v>3.000123538674034</v>
+        <v>3.001976565304254</v>
       </c>
     </row>
     <row r="516">
@@ -21597,7 +21597,7 @@
         <v>13</v>
       </c>
       <c r="K516" t="n">
-        <v>2.985196509743719</v>
+        <v>2.985675242438017</v>
       </c>
     </row>
     <row r="517">
@@ -21638,7 +21638,7 @@
         <v>13</v>
       </c>
       <c r="K517" t="n">
-        <v>2.898965855214034</v>
+        <v>2.899675901758939</v>
       </c>
     </row>
     <row r="518">
@@ -21679,7 +21679,7 @@
         <v>13</v>
       </c>
       <c r="K518" t="n">
-        <v>2.866411525978028</v>
+        <v>2.869457509158303</v>
       </c>
     </row>
     <row r="519">
@@ -21720,7 +21720,7 @@
         <v>13</v>
       </c>
       <c r="K519" t="n">
-        <v>2.804442518326792</v>
+        <v>2.804729380677165</v>
       </c>
     </row>
     <row r="520">
@@ -21761,7 +21761,7 @@
         <v>13</v>
       </c>
       <c r="K520" t="n">
-        <v>2.793368342944497</v>
+        <v>2.793088229186607</v>
       </c>
     </row>
     <row r="521">
@@ -21802,7 +21802,7 @@
         <v>13</v>
       </c>
       <c r="K521" t="n">
-        <v>2.8344944933717</v>
+        <v>2.83400216755078</v>
       </c>
     </row>
     <row r="522">
@@ -21843,7 +21843,7 @@
         <v>13</v>
       </c>
       <c r="K522" t="n">
-        <v>2.978694410001666</v>
+        <v>2.978051513855749</v>
       </c>
     </row>
     <row r="523">
@@ -21884,7 +21884,7 @@
         <v>13</v>
       </c>
       <c r="K523" t="n">
-        <v>3.159334697262127</v>
+        <v>3.155365033622441</v>
       </c>
     </row>
     <row r="524">
@@ -21925,7 +21925,7 @@
         <v>13</v>
       </c>
       <c r="K524" t="n">
-        <v>3.190147370379927</v>
+        <v>3.189312340487478</v>
       </c>
     </row>
     <row r="525">
@@ -21966,7 +21966,7 @@
         <v>13</v>
       </c>
       <c r="K525" t="n">
-        <v>3.225654916860527</v>
+        <v>3.222418768578666</v>
       </c>
     </row>
     <row r="526">
@@ -22007,7 +22007,7 @@
         <v>13</v>
       </c>
       <c r="K526" t="n">
-        <v>3.324263247984628</v>
+        <v>3.32396463946663</v>
       </c>
     </row>
     <row r="527">
@@ -22048,7 +22048,7 @@
         <v>13</v>
       </c>
       <c r="K527" t="n">
-        <v>3.324263247984628</v>
+        <v>3.32396463946663</v>
       </c>
     </row>
     <row r="528">
@@ -22089,7 +22089,7 @@
         <v>13</v>
       </c>
       <c r="K528" t="n">
-        <v>3.335443735846939</v>
+        <v>3.334501763034719</v>
       </c>
     </row>
     <row r="529">
@@ -22130,7 +22130,7 @@
         <v>13</v>
       </c>
       <c r="K529" t="n">
-        <v>3.354488749407895</v>
+        <v>3.354225595015699</v>
       </c>
     </row>
     <row r="530">
@@ -22171,7 +22171,7 @@
         <v>13</v>
       </c>
       <c r="K530" t="n">
-        <v>3.354488749407895</v>
+        <v>3.354225595015699</v>
       </c>
     </row>
     <row r="531">
@@ -22212,7 +22212,7 @@
         <v>13</v>
       </c>
       <c r="K531" t="n">
-        <v>3.355785424906909</v>
+        <v>3.355767510687288</v>
       </c>
     </row>
     <row r="532">
@@ -22253,7 +22253,7 @@
         <v>13</v>
       </c>
       <c r="K532" t="n">
-        <v>3.341758932342058</v>
+        <v>3.341852322842519</v>
       </c>
     </row>
     <row r="533">
@@ -22294,7 +22294,7 @@
         <v>13</v>
       </c>
       <c r="K533" t="n">
-        <v>3.330932356619231</v>
+        <v>3.330907880328162</v>
       </c>
     </row>
     <row r="534">
@@ -22335,7 +22335,7 @@
         <v>13</v>
       </c>
       <c r="K534" t="n">
-        <v>3.327986602900669</v>
+        <v>3.328375725233958</v>
       </c>
     </row>
     <row r="535">
@@ -22376,7 +22376,7 @@
         <v>13</v>
       </c>
       <c r="K535" t="n">
-        <v>3.275139678285788</v>
+        <v>3.277374525780483</v>
       </c>
     </row>
     <row r="536">
@@ -22417,7 +22417,7 @@
         <v>13</v>
       </c>
       <c r="K536" t="n">
-        <v>3.230262931772916</v>
+        <v>3.232133431624247</v>
       </c>
     </row>
     <row r="537">
@@ -22458,7 +22458,7 @@
         <v>13</v>
       </c>
       <c r="K537" t="n">
-        <v>3.131886002261335</v>
+        <v>3.133613835412002</v>
       </c>
     </row>
     <row r="538">
@@ -22499,7 +22499,7 @@
         <v>13</v>
       </c>
       <c r="K538" t="n">
-        <v>3.080393039227168</v>
+        <v>3.080715713525164</v>
       </c>
     </row>
     <row r="539">
@@ -22540,7 +22540,7 @@
         <v>13</v>
       </c>
       <c r="K539" t="n">
-        <v>3.026387919377109</v>
+        <v>3.026415980916592</v>
       </c>
     </row>
     <row r="540">
@@ -22581,7 +22581,7 @@
         <v>13</v>
       </c>
       <c r="K540" t="n">
-        <v>3.025961770567625</v>
+        <v>3.025920799104895</v>
       </c>
     </row>
     <row r="541">
@@ -22622,7 +22622,7 @@
         <v>13</v>
       </c>
       <c r="K541" t="n">
-        <v>3.027961999470983</v>
+        <v>3.027949019687921</v>
       </c>
     </row>
     <row r="542">
@@ -22663,7 +22663,7 @@
         <v>13</v>
       </c>
       <c r="K542" t="n">
-        <v>3.026468294415091</v>
+        <v>3.026525082901294</v>
       </c>
     </row>
     <row r="543">
@@ -22704,7 +22704,7 @@
         <v>13</v>
       </c>
       <c r="K543" t="n">
-        <v>3.013936903687413</v>
+        <v>3.014079227476111</v>
       </c>
     </row>
     <row r="544">
@@ -22745,7 +22745,7 @@
         <v>13</v>
       </c>
       <c r="K544" t="n">
-        <v>3.046001730585111</v>
+        <v>3.043954329394944</v>
       </c>
     </row>
     <row r="545">
@@ -22786,7 +22786,7 @@
         <v>13</v>
       </c>
       <c r="K545" t="n">
-        <v>3.112539011476911</v>
+        <v>3.112049976126367</v>
       </c>
     </row>
     <row r="546">
@@ -22827,7 +22827,7 @@
         <v>13</v>
       </c>
       <c r="K546" t="n">
-        <v>3.112539011476911</v>
+        <v>3.112049976126367</v>
       </c>
     </row>
     <row r="547">
@@ -22868,7 +22868,7 @@
         <v>13</v>
       </c>
       <c r="K547" t="n">
-        <v>3.156988090616639</v>
+        <v>3.156628573026361</v>
       </c>
     </row>
     <row r="548">
@@ -22909,7 +22909,7 @@
         <v>13</v>
       </c>
       <c r="K548" t="n">
-        <v>3.161312492740686</v>
+        <v>3.161826064235211</v>
       </c>
     </row>
     <row r="549">
@@ -22950,7 +22950,7 @@
         <v>13</v>
       </c>
       <c r="K549" t="n">
-        <v>3.152328710565331</v>
+        <v>3.152820475796155</v>
       </c>
     </row>
     <row r="550">
@@ -22991,7 +22991,7 @@
         <v>13</v>
       </c>
       <c r="K550" t="n">
-        <v>3.148341453637074</v>
+        <v>3.148369285656599</v>
       </c>
     </row>
     <row r="551">
@@ -23032,7 +23032,7 @@
         <v>13</v>
       </c>
       <c r="K551" t="n">
-        <v>3.114722228660195</v>
+        <v>3.115008312947572</v>
       </c>
     </row>
     <row r="552">
@@ -23073,7 +23073,7 @@
         <v>13</v>
       </c>
       <c r="K552" t="n">
-        <v>3.114722228660195</v>
+        <v>3.115008312947572</v>
       </c>
     </row>
     <row r="553">
@@ -23114,7 +23114,7 @@
         <v>13</v>
       </c>
       <c r="K553" t="n">
-        <v>3.079325703913772</v>
+        <v>3.079678497670573</v>
       </c>
     </row>
     <row r="554">
@@ -23155,7 +23155,7 @@
         <v>13</v>
       </c>
       <c r="K554" t="n">
-        <v>3.039807136754343</v>
+        <v>3.04029692814976</v>
       </c>
     </row>
     <row r="555">
@@ -23196,7 +23196,7 @@
         <v>13</v>
       </c>
       <c r="K555" t="n">
-        <v>2.902229781513417</v>
+        <v>2.902846773643245</v>
       </c>
     </row>
     <row r="556">
@@ -23237,7 +23237,7 @@
         <v>13</v>
       </c>
       <c r="K556" t="n">
-        <v>2.859260866039956</v>
+        <v>2.863345595493815</v>
       </c>
     </row>
     <row r="557">
@@ -23278,7 +23278,7 @@
         <v>13</v>
       </c>
       <c r="K557" t="n">
-        <v>2.781104496918592</v>
+        <v>2.785017635806245</v>
       </c>
     </row>
     <row r="558">
@@ -23319,7 +23319,7 @@
         <v>13</v>
       </c>
       <c r="K558" t="n">
-        <v>2.781104496918592</v>
+        <v>2.785017635806245</v>
       </c>
     </row>
     <row r="559">
@@ -23360,7 +23360,7 @@
         <v>13</v>
       </c>
       <c r="K559" t="n">
-        <v>2.781104496918592</v>
+        <v>2.785017635806245</v>
       </c>
     </row>
     <row r="560">
@@ -23401,7 +23401,7 @@
         <v>13</v>
       </c>
       <c r="K560" t="n">
-        <v>2.746235642534695</v>
+        <v>2.746766811742448</v>
       </c>
     </row>
     <row r="561">
@@ -23442,7 +23442,7 @@
         <v>13</v>
       </c>
       <c r="K561" t="n">
-        <v>2.709446003344465</v>
+        <v>2.712874560441837</v>
       </c>
     </row>
     <row r="562">
@@ -23483,7 +23483,7 @@
         <v>13</v>
       </c>
       <c r="K562" t="n">
-        <v>2.679965085625929</v>
+        <v>2.680357631595343</v>
       </c>
     </row>
     <row r="563">
@@ -23524,7 +23524,7 @@
         <v>13</v>
       </c>
       <c r="K563" t="n">
-        <v>2.614988202137864</v>
+        <v>2.615437609449622</v>
       </c>
     </row>
     <row r="564">
@@ -23565,7 +23565,7 @@
         <v>13</v>
       </c>
       <c r="K564" t="n">
-        <v>2.575281413579709</v>
+        <v>2.579534413252021</v>
       </c>
     </row>
     <row r="565">
@@ -23606,7 +23606,7 @@
         <v>13</v>
       </c>
       <c r="K565" t="n">
-        <v>2.410250010654948</v>
+        <v>2.414573439729309</v>
       </c>
     </row>
     <row r="566">
@@ -23647,7 +23647,7 @@
         <v>13</v>
       </c>
       <c r="K566" t="n">
-        <v>2.30555945230456</v>
+        <v>2.305986943031564</v>
       </c>
     </row>
     <row r="567">
@@ -23688,7 +23688,7 @@
         <v>13</v>
       </c>
       <c r="K567" t="n">
-        <v>2.256654538307345</v>
+        <v>2.258329967628628</v>
       </c>
     </row>
     <row r="568">
@@ -23729,7 +23729,7 @@
         <v>13</v>
       </c>
       <c r="K568" t="n">
-        <v>2.205072985932964</v>
+        <v>2.206752089319624</v>
       </c>
     </row>
     <row r="569">
@@ -23770,7 +23770,7 @@
         <v>13</v>
       </c>
       <c r="K569" t="n">
-        <v>2.184464599870547</v>
+        <v>2.183805021788351</v>
       </c>
     </row>
     <row r="570">
@@ -23811,7 +23811,7 @@
         <v>13</v>
       </c>
       <c r="K570" t="n">
-        <v>2.188212485394808</v>
+        <v>2.188194325195013</v>
       </c>
     </row>
     <row r="571">
@@ -23852,7 +23852,7 @@
         <v>13</v>
       </c>
       <c r="K571" t="n">
-        <v>2.289890605254381</v>
+        <v>2.281002782139863</v>
       </c>
     </row>
     <row r="572">
@@ -23893,7 +23893,7 @@
         <v>13</v>
       </c>
       <c r="K572" t="n">
-        <v>2.397986819953942</v>
+        <v>2.389303026336055</v>
       </c>
     </row>
     <row r="573">
@@ -23934,7 +23934,7 @@
         <v>13</v>
       </c>
       <c r="K573" t="n">
-        <v>2.882020044560333</v>
+        <v>2.878739002188572</v>
       </c>
     </row>
     <row r="574">
@@ -23975,7 +23975,7 @@
         <v>13</v>
       </c>
       <c r="K574" t="n">
-        <v>3.069935697821208</v>
+        <v>3.061794405760153</v>
       </c>
     </row>
     <row r="575">
@@ -24016,7 +24016,7 @@
         <v>13</v>
       </c>
       <c r="K575" t="n">
-        <v>3.955345534259584</v>
+        <v>3.954291549224395</v>
       </c>
     </row>
     <row r="576">
@@ -24057,7 +24057,7 @@
         <v>13</v>
       </c>
       <c r="K576" t="n">
-        <v>3.929530787195231</v>
+        <v>3.924958658994567</v>
       </c>
     </row>
     <row r="577">
@@ -24098,7 +24098,7 @@
         <v>13</v>
       </c>
       <c r="K577" t="n">
-        <v>4.328714338131201</v>
+        <v>4.320531525053801</v>
       </c>
     </row>
     <row r="578">
@@ -24139,7 +24139,7 @@
         <v>13</v>
       </c>
       <c r="K578" t="n">
-        <v>4.328714338131201</v>
+        <v>4.320531525053801</v>
       </c>
     </row>
     <row r="579">
@@ -24180,7 +24180,7 @@
         <v>13</v>
       </c>
       <c r="K579" t="n">
-        <v>4.531671110329528</v>
+        <v>4.526950727777223</v>
       </c>
     </row>
     <row r="580">
@@ -24221,7 +24221,7 @@
         <v>13</v>
       </c>
       <c r="K580" t="n">
-        <v>4.592091779282402</v>
+        <v>4.623524448590813</v>
       </c>
     </row>
     <row r="581">
@@ -24262,7 +24262,7 @@
         <v>13</v>
       </c>
       <c r="K581" t="n">
-        <v>4.623903295780982</v>
+        <v>4.623524448590813</v>
       </c>
     </row>
     <row r="582">
@@ -24303,7 +24303,7 @@
         <v>13</v>
       </c>
       <c r="K582" t="n">
-        <v>4.623903295780982</v>
+        <v>4.623524448590813</v>
       </c>
     </row>
     <row r="583">
@@ -24344,7 +24344,7 @@
         <v>13</v>
       </c>
       <c r="K583" t="n">
-        <v>4.644597238575603</v>
+        <v>4.63638824025024</v>
       </c>
     </row>
     <row r="584">
@@ -24385,7 +24385,7 @@
         <v>13</v>
       </c>
       <c r="K584" t="n">
-        <v>4.644597238575603</v>
+        <v>4.63638824025024</v>
       </c>
     </row>
     <row r="585">
@@ -24426,7 +24426,7 @@
         <v>13</v>
       </c>
       <c r="K585" t="n">
-        <v>4.603201230477512</v>
+        <v>4.572101112282842</v>
       </c>
     </row>
     <row r="586">
@@ -24467,7 +24467,7 @@
         <v>13</v>
       </c>
       <c r="K586" t="n">
-        <v>4.472780263516613</v>
+        <v>4.297069666275996</v>
       </c>
     </row>
     <row r="587">
@@ -24508,7 +24508,7 @@
         <v>13</v>
       </c>
       <c r="K587" t="n">
-        <v>4.275816844095338</v>
+        <v>4.297069666275996</v>
       </c>
     </row>
     <row r="588">
@@ -24549,7 +24549,7 @@
         <v>13</v>
       </c>
       <c r="K588" t="n">
-        <v>4.275816844095338</v>
+        <v>4.297069666275996</v>
       </c>
     </row>
     <row r="589">
@@ -24590,7 +24590,7 @@
         <v>13</v>
       </c>
       <c r="K589" t="n">
-        <v>4.275816844095338</v>
+        <v>4.297069666275996</v>
       </c>
     </row>
     <row r="590">
@@ -24631,7 +24631,7 @@
         <v>13</v>
       </c>
       <c r="K590" t="n">
-        <v>4.033548448337522</v>
+        <v>4.062687804356615</v>
       </c>
     </row>
     <row r="591">
@@ -24672,7 +24672,7 @@
         <v>13</v>
       </c>
       <c r="K591" t="n">
-        <v>4.001625869019882</v>
+        <v>4.017214497603873</v>
       </c>
     </row>
     <row r="592">
@@ -24713,7 +24713,7 @@
         <v>13</v>
       </c>
       <c r="K592" t="n">
-        <v>4.001625869019882</v>
+        <v>4.017214497603873</v>
       </c>
     </row>
     <row r="593">
@@ -24754,7 +24754,7 @@
         <v>13</v>
       </c>
       <c r="K593" t="n">
-        <v>4.050633778591138</v>
+        <v>4.040050583440248</v>
       </c>
     </row>
     <row r="594">
@@ -24795,7 +24795,7 @@
         <v>13</v>
       </c>
       <c r="K594" t="n">
-        <v>4.050633778591138</v>
+        <v>4.040050583440248</v>
       </c>
     </row>
     <row r="595">
@@ -24836,7 +24836,7 @@
         <v>13</v>
       </c>
       <c r="K595" t="n">
-        <v>4.354814061134852</v>
+        <v>4.408678722612856</v>
       </c>
     </row>
     <row r="596">
@@ -24877,7 +24877,7 @@
         <v>13</v>
       </c>
       <c r="K596" t="n">
-        <v>4.354814061134852</v>
+        <v>4.408678722612856</v>
       </c>
     </row>
     <row r="597">
@@ -24918,7 +24918,7 @@
         <v>13</v>
       </c>
       <c r="K597" t="n">
-        <v>4.683157014231064</v>
+        <v>4.744924889868029</v>
       </c>
     </row>
     <row r="598">
@@ -24959,7 +24959,7 @@
         <v>13</v>
       </c>
       <c r="K598" t="n">
-        <v>4.683157014231064</v>
+        <v>4.744924889868029</v>
       </c>
     </row>
     <row r="599">
@@ -25000,7 +25000,7 @@
         <v>13</v>
       </c>
       <c r="K599" t="n">
-        <v>4.683157014231064</v>
+        <v>4.744924889868029</v>
       </c>
     </row>
     <row r="600">
@@ -25041,7 +25041,7 @@
         <v>13</v>
       </c>
       <c r="K600" t="n">
-        <v>5.664239153404013</v>
+        <v>5.578339670673344</v>
       </c>
     </row>
     <row r="601">
@@ -25082,7 +25082,7 @@
         <v>13</v>
       </c>
       <c r="K601" t="n">
-        <v>5.664239153404013</v>
+        <v>5.807255290542151</v>
       </c>
     </row>
     <row r="602">
@@ -25123,7 +25123,7 @@
         <v>13</v>
       </c>
       <c r="K602" t="n">
-        <v>5.886263841702769</v>
+        <v>5.807255290542151</v>
       </c>
     </row>
     <row r="603">
@@ -25164,7 +25164,7 @@
         <v>13</v>
       </c>
       <c r="K603" t="n">
-        <v>3.55762417043264</v>
+        <v>3.577921702813618</v>
       </c>
     </row>
     <row r="604">
@@ -25205,7 +25205,7 @@
         <v>13</v>
       </c>
       <c r="K604" t="n">
-        <v>2.304263759799705</v>
+        <v>2.320302541898265</v>
       </c>
     </row>
     <row r="605">
@@ -25246,7 +25246,7 @@
         <v>13</v>
       </c>
       <c r="K605" t="n">
-        <v>2.304263759799705</v>
+        <v>2.320302541898265</v>
       </c>
     </row>
     <row r="606">
@@ -25287,7 +25287,7 @@
         <v>13</v>
       </c>
       <c r="K606" t="n">
-        <v>2.007517432564142</v>
+        <v>2.011095696284843</v>
       </c>
     </row>
     <row r="607">
@@ -25328,7 +25328,7 @@
         <v>13</v>
       </c>
       <c r="K607" t="n">
-        <v>1.867009997583336</v>
+        <v>1.866190028464348</v>
       </c>
     </row>
     <row r="608">
@@ -25369,7 +25369,7 @@
         <v>13</v>
       </c>
       <c r="K608" t="n">
-        <v>1.867009997583336</v>
+        <v>1.866190028464348</v>
       </c>
     </row>
     <row r="609">
@@ -25410,7 +25410,7 @@
         <v>13</v>
       </c>
       <c r="K609" t="n">
-        <v>1.96218740185479</v>
+        <v>1.960375935775285</v>
       </c>
     </row>
     <row r="610">
@@ -25451,7 +25451,7 @@
         <v>13</v>
       </c>
       <c r="K610" t="n">
-        <v>2.062267475260988</v>
+        <v>2.06000630112602</v>
       </c>
     </row>
     <row r="611">
@@ -25492,7 +25492,7 @@
         <v>13</v>
       </c>
       <c r="K611" t="n">
-        <v>2.265887516607968</v>
+        <v>2.263364774596643</v>
       </c>
     </row>
     <row r="612">
@@ -25533,7 +25533,7 @@
         <v>13</v>
       </c>
       <c r="K612" t="n">
-        <v>2.397945623303229</v>
+        <v>2.395295320458675</v>
       </c>
     </row>
     <row r="613">
@@ -25574,7 +25574,7 @@
         <v>13</v>
       </c>
       <c r="K613" t="n">
-        <v>2.496399929876021</v>
+        <v>2.493111610048887</v>
       </c>
     </row>
     <row r="614">
@@ -25615,7 +25615,7 @@
         <v>13</v>
       </c>
       <c r="K614" t="n">
-        <v>2.636400685014193</v>
+        <v>2.635034458652775</v>
       </c>
     </row>
     <row r="615">
@@ -25656,7 +25656,7 @@
         <v>13</v>
       </c>
       <c r="K615" t="n">
-        <v>2.745146212524012</v>
+        <v>2.746100288452091</v>
       </c>
     </row>
     <row r="616">
@@ -25697,7 +25697,7 @@
         <v>13</v>
       </c>
       <c r="K616" t="n">
-        <v>2.745146212524012</v>
+        <v>2.746100288452091</v>
       </c>
     </row>
     <row r="617">
@@ -25738,7 +25738,7 @@
         <v>13</v>
       </c>
       <c r="K617" t="n">
-        <v>2.663751785453709</v>
+        <v>2.664277380462285</v>
       </c>
     </row>
     <row r="618">
@@ -25779,7 +25779,7 @@
         <v>13</v>
       </c>
       <c r="K618" t="n">
-        <v>2.663751785453709</v>
+        <v>2.664277380462285</v>
       </c>
     </row>
     <row r="619">
@@ -25820,7 +25820,7 @@
         <v>13</v>
       </c>
       <c r="K619" t="n">
-        <v>2.619227586427406</v>
+        <v>2.6214035384454</v>
       </c>
     </row>
     <row r="620">
@@ -25861,7 +25861,7 @@
         <v>13</v>
       </c>
       <c r="K620" t="n">
-        <v>2.53626736395919</v>
+        <v>2.538849247660146</v>
       </c>
     </row>
     <row r="621">
@@ -25902,7 +25902,7 @@
         <v>13</v>
       </c>
       <c r="K621" t="n">
-        <v>2.53626736395919</v>
+        <v>2.538849247660146</v>
       </c>
     </row>
     <row r="622">
@@ -25943,7 +25943,7 @@
         <v>13</v>
       </c>
       <c r="K622" t="n">
-        <v>2.53626736395919</v>
+        <v>2.538849247660146</v>
       </c>
     </row>
     <row r="623">
@@ -25984,7 +25984,7 @@
         <v>13</v>
       </c>
       <c r="K623" t="n">
-        <v>2.465248009109999</v>
+        <v>2.46614663472738</v>
       </c>
     </row>
     <row r="624">
@@ -26025,7 +26025,7 @@
         <v>13</v>
       </c>
       <c r="K624" t="n">
-        <v>2.374366744816958</v>
+        <v>2.372973910694888</v>
       </c>
     </row>
     <row r="625">
@@ -26066,7 +26066,7 @@
         <v>13</v>
       </c>
       <c r="K625" t="n">
-        <v>2.374366744816958</v>
+        <v>2.372973910694888</v>
       </c>
     </row>
     <row r="626">
@@ -26107,7 +26107,7 @@
         <v>13</v>
       </c>
       <c r="K626" t="n">
-        <v>2.386992352478341</v>
+        <v>2.386104872458675</v>
       </c>
     </row>
     <row r="627">
@@ -26148,7 +26148,7 @@
         <v>13</v>
       </c>
       <c r="K627" t="n">
-        <v>2.386992352478341</v>
+        <v>2.386104872458675</v>
       </c>
     </row>
     <row r="628">
@@ -26189,7 +26189,7 @@
         <v>13</v>
       </c>
       <c r="K628" t="n">
-        <v>2.33991266042025</v>
+        <v>2.339378134951555</v>
       </c>
     </row>
     <row r="629">
@@ -26230,7 +26230,7 @@
         <v>13</v>
       </c>
       <c r="K629" t="n">
-        <v>2.375648316981637</v>
+        <v>2.375575370680345</v>
       </c>
     </row>
     <row r="630">
@@ -26271,7 +26271,7 @@
         <v>13</v>
       </c>
       <c r="K630" t="n">
-        <v>2.50679042595434</v>
+        <v>2.505941600271696</v>
       </c>
     </row>
     <row r="631">
@@ -26312,7 +26312,7 @@
         <v>13</v>
       </c>
       <c r="K631" t="n">
-        <v>2.50679042595434</v>
+        <v>2.505941600271696</v>
       </c>
     </row>
     <row r="632">
@@ -26353,7 +26353,7 @@
         <v>13</v>
       </c>
       <c r="K632" t="n">
-        <v>2.50679042595434</v>
+        <v>2.505941600271696</v>
       </c>
     </row>
     <row r="633">
@@ -26394,7 +26394,7 @@
         <v>13</v>
       </c>
       <c r="K633" t="n">
-        <v>2.520281166940428</v>
+        <v>2.520168091692119</v>
       </c>
     </row>
     <row r="634">
@@ -26435,7 +26435,7 @@
         <v>13</v>
       </c>
       <c r="K634" t="n">
-        <v>2.506770776921634</v>
+        <v>2.506667399990243</v>
       </c>
     </row>
     <row r="635">
@@ -26476,7 +26476,7 @@
         <v>13</v>
       </c>
       <c r="K635" t="n">
-        <v>2.500508165998939</v>
+        <v>2.500244280307097</v>
       </c>
     </row>
     <row r="636">
@@ -26517,7 +26517,7 @@
         <v>13</v>
       </c>
       <c r="K636" t="n">
-        <v>2.513878929166006</v>
+        <v>2.51478147785248</v>
       </c>
     </row>
     <row r="637">
@@ -26558,7 +26558,7 @@
         <v>13</v>
       </c>
       <c r="K637" t="n">
-        <v>2.513878929166006</v>
+        <v>2.51478147785248</v>
       </c>
     </row>
     <row r="638">
@@ -26599,7 +26599,7 @@
         <v>13</v>
       </c>
       <c r="K638" t="n">
-        <v>2.459474258732532</v>
+        <v>2.463497413717138</v>
       </c>
     </row>
     <row r="639">
@@ -26640,7 +26640,7 @@
         <v>13</v>
       </c>
       <c r="K639" t="n">
-        <v>2.259434093810857</v>
+        <v>2.267683125535719</v>
       </c>
     </row>
     <row r="640">
@@ -26681,7 +26681,7 @@
         <v>13</v>
       </c>
       <c r="K640" t="n">
-        <v>2.259434093810857</v>
+        <v>2.267683125535719</v>
       </c>
     </row>
     <row r="641">
@@ -26722,7 +26722,7 @@
         <v>13</v>
       </c>
       <c r="K641" t="n">
-        <v>2.176262567856492</v>
+        <v>2.17714257085892</v>
       </c>
     </row>
     <row r="642">
@@ -26763,7 +26763,7 @@
         <v>13</v>
       </c>
       <c r="K642" t="n">
-        <v>2.176262567856492</v>
+        <v>2.17714257085892</v>
       </c>
     </row>
     <row r="643">
@@ -26804,7 +26804,7 @@
         <v>13</v>
       </c>
       <c r="K643" t="n">
-        <v>2.154915804113018</v>
+        <v>2.160355411637962</v>
       </c>
     </row>
     <row r="644">
@@ -26845,7 +26845,7 @@
         <v>13</v>
       </c>
       <c r="K644" t="n">
-        <v>2.172438846071022</v>
+        <v>2.17696441275093</v>
       </c>
     </row>
     <row r="645">
@@ -26886,7 +26886,7 @@
         <v>13</v>
       </c>
       <c r="K645" t="n">
-        <v>2.095712248255831</v>
+        <v>2.095207111296562</v>
       </c>
     </row>
     <row r="646">
@@ -26927,7 +26927,7 @@
         <v>13</v>
       </c>
       <c r="K646" t="n">
-        <v>2.072854197353094</v>
+        <v>2.073423997008935</v>
       </c>
     </row>
     <row r="647">
@@ -26968,7 +26968,7 @@
         <v>13</v>
       </c>
       <c r="K647" t="n">
-        <v>1.969261619638404</v>
+        <v>1.970873500979873</v>
       </c>
     </row>
     <row r="648">
@@ -27009,7 +27009,7 @@
         <v>13</v>
       </c>
       <c r="K648" t="n">
-        <v>1.884782537198478</v>
+        <v>1.885147569802867</v>
       </c>
     </row>
     <row r="649">
@@ -27050,7 +27050,7 @@
         <v>13</v>
       </c>
       <c r="K649" t="n">
-        <v>1.884782537198478</v>
+        <v>1.885147569802867</v>
       </c>
     </row>
     <row r="650">
@@ -27091,7 +27091,7 @@
         <v>13</v>
       </c>
       <c r="K650" t="n">
-        <v>1.884782537198478</v>
+        <v>1.885147569802867</v>
       </c>
     </row>
     <row r="651">
@@ -27132,7 +27132,7 @@
         <v>13</v>
       </c>
       <c r="K651" t="n">
-        <v>1.851905154232513</v>
+        <v>1.852263272850365</v>
       </c>
     </row>
     <row r="652">
@@ -27173,7 +27173,7 @@
         <v>13</v>
       </c>
       <c r="K652" t="n">
-        <v>1.851905154232513</v>
+        <v>1.852263272850365</v>
       </c>
     </row>
     <row r="653">
@@ -27214,7 +27214,7 @@
         <v>13</v>
       </c>
       <c r="K653" t="n">
-        <v>1.904687667945801</v>
+        <v>1.903631966647837</v>
       </c>
     </row>
     <row r="654">
@@ -27255,7 +27255,7 @@
         <v>13</v>
       </c>
       <c r="K654" t="n">
-        <v>1.904687667945801</v>
+        <v>1.903631966647837</v>
       </c>
     </row>
     <row r="655">
@@ -27296,7 +27296,7 @@
         <v>13</v>
       </c>
       <c r="K655" t="n">
-        <v>1.896609628078574</v>
+        <v>1.89757818046697</v>
       </c>
     </row>
     <row r="656">
@@ -27337,7 +27337,7 @@
         <v>13</v>
       </c>
       <c r="K656" t="n">
-        <v>1.801946230465687</v>
+        <v>1.80214187997295</v>
       </c>
     </row>
     <row r="657">
@@ -27378,7 +27378,7 @@
         <v>13</v>
       </c>
       <c r="K657" t="n">
-        <v>1.801946230465687</v>
+        <v>1.80214187997295</v>
       </c>
     </row>
     <row r="658">
@@ -27419,7 +27419,7 @@
         <v>13</v>
       </c>
       <c r="K658" t="n">
-        <v>1.802843650038023</v>
+        <v>1.802665241206594</v>
       </c>
     </row>
     <row r="659">
@@ -27460,7 +27460,7 @@
         <v>13</v>
       </c>
       <c r="K659" t="n">
-        <v>1.821306136060561</v>
+        <v>1.81985405216377</v>
       </c>
     </row>
     <row r="660">
@@ -27501,7 +27501,7 @@
         <v>13</v>
       </c>
       <c r="K660" t="n">
-        <v>1.882631057977212</v>
+        <v>1.880480522627099</v>
       </c>
     </row>
     <row r="661">
@@ -27542,7 +27542,7 @@
         <v>13</v>
       </c>
       <c r="K661" t="n">
-        <v>1.964692191183084</v>
+        <v>1.963393270212991</v>
       </c>
     </row>
     <row r="662">
@@ -27583,7 +27583,7 @@
         <v>13</v>
       </c>
       <c r="K662" t="n">
-        <v>1.908081894797122</v>
+        <v>1.910196243707518</v>
       </c>
     </row>
     <row r="663">
@@ -27624,7 +27624,7 @@
         <v>13</v>
       </c>
       <c r="K663" t="n">
-        <v>1.813280388812845</v>
+        <v>1.81613474301318</v>
       </c>
     </row>
     <row r="664">
@@ -27665,7 +27665,7 @@
         <v>13</v>
       </c>
       <c r="K664" t="n">
-        <v>1.813280388812845</v>
+        <v>1.81613474301318</v>
       </c>
     </row>
     <row r="665">
@@ -27706,7 +27706,7 @@
         <v>13</v>
       </c>
       <c r="K665" t="n">
-        <v>1.702954595778851</v>
+        <v>1.706535450860557</v>
       </c>
     </row>
     <row r="666">
@@ -27747,7 +27747,7 @@
         <v>13</v>
       </c>
       <c r="K666" t="n">
-        <v>1.451522606745209</v>
+        <v>1.452508443369184</v>
       </c>
     </row>
     <row r="667">
@@ -27788,7 +27788,7 @@
         <v>13</v>
       </c>
       <c r="K667" t="n">
-        <v>1.392740740496996</v>
+        <v>1.392357685497432</v>
       </c>
     </row>
     <row r="668">
@@ -27829,7 +27829,7 @@
         <v>13</v>
       </c>
       <c r="K668" t="n">
-        <v>1.392740740496996</v>
+        <v>1.392357685497432</v>
       </c>
     </row>
     <row r="669">
@@ -27870,7 +27870,7 @@
         <v>13</v>
       </c>
       <c r="K669" t="n">
-        <v>1.238234855147982</v>
+        <v>1.237747043511612</v>
       </c>
     </row>
     <row r="670">
@@ -27911,7 +27911,7 @@
         <v>13</v>
       </c>
       <c r="K670" t="n">
-        <v>1.238234855147982</v>
+        <v>1.237747043511612</v>
       </c>
     </row>
     <row r="671">
@@ -27952,7 +27952,7 @@
         <v>13</v>
       </c>
       <c r="K671" t="n">
-        <v>1.463830566330504</v>
+        <v>1.461942149642087</v>
       </c>
     </row>
     <row r="672">
@@ -27993,7 +27993,7 @@
         <v>13</v>
       </c>
       <c r="K672" t="n">
-        <v>1.532244366196418</v>
+        <v>1.532597244509347</v>
       </c>
     </row>
     <row r="673">
@@ -28034,7 +28034,7 @@
         <v>13</v>
       </c>
       <c r="K673" t="n">
-        <v>1.527756290070972</v>
+        <v>1.527597272839859</v>
       </c>
     </row>
     <row r="674">
@@ -28075,7 +28075,7 @@
         <v>13</v>
       </c>
       <c r="K674" t="n">
-        <v>1.527756290070972</v>
+        <v>1.527597272839859</v>
       </c>
     </row>
     <row r="675">
@@ -28116,7 +28116,7 @@
         <v>13</v>
       </c>
       <c r="K675" t="n">
-        <v>1.520022086752104</v>
+        <v>1.520249201757672</v>
       </c>
     </row>
     <row r="676">
@@ -28157,7 +28157,7 @@
         <v>13</v>
       </c>
       <c r="K676" t="n">
-        <v>1.50921825878724</v>
+        <v>1.510252951969479</v>
       </c>
     </row>
     <row r="677">
@@ -28198,7 +28198,7 @@
         <v>13</v>
       </c>
       <c r="K677" t="n">
-        <v>1.462574299215829</v>
+        <v>1.463671582411677</v>
       </c>
     </row>
     <row r="678">
@@ -28239,7 +28239,7 @@
         <v>13</v>
       </c>
       <c r="K678" t="n">
-        <v>1.416270653651503</v>
+        <v>1.417750406489253</v>
       </c>
     </row>
     <row r="679">
@@ -28280,7 +28280,7 @@
         <v>13</v>
       </c>
       <c r="K679" t="n">
-        <v>1.3576163928357</v>
+        <v>1.358934406790085</v>
       </c>
     </row>
     <row r="680">
@@ -28321,7 +28321,7 @@
         <v>13</v>
       </c>
       <c r="K680" t="n">
-        <v>1.30804719163141</v>
+        <v>1.30915797599857</v>
       </c>
     </row>
     <row r="681">
@@ -28362,7 +28362,7 @@
         <v>13</v>
       </c>
       <c r="K681" t="n">
-        <v>1.259396699527863</v>
+        <v>1.26089352957117</v>
       </c>
     </row>
     <row r="682">
@@ -28403,7 +28403,7 @@
         <v>13</v>
       </c>
       <c r="K682" t="n">
-        <v>0.9659556134910596</v>
+        <v>0.9690210022968986</v>
       </c>
     </row>
     <row r="683">
@@ -28444,7 +28444,7 @@
         <v>13</v>
       </c>
       <c r="K683" t="n">
-        <v>0.6083743863731486</v>
+        <v>0.6081488177763253</v>
       </c>
     </row>
     <row r="684">
@@ -28485,7 +28485,7 @@
         <v>13</v>
       </c>
       <c r="K684" t="n">
-        <v>0.6083743863731486</v>
+        <v>0.6081488177763253</v>
       </c>
     </row>
     <row r="685">
@@ -28526,7 +28526,7 @@
         <v>13</v>
       </c>
       <c r="K685" t="n">
-        <v>1.02377229359855</v>
+        <v>1.020558393787915</v>
       </c>
     </row>
     <row r="686">
@@ -28567,7 +28567,7 @@
         <v>13</v>
       </c>
       <c r="K686" t="n">
-        <v>1.130287444594395</v>
+        <v>1.128197722757464</v>
       </c>
     </row>
     <row r="687">
@@ -28608,7 +28608,7 @@
         <v>13</v>
       </c>
       <c r="K687" t="n">
-        <v>1.130287444594395</v>
+        <v>1.128197722757464</v>
       </c>
     </row>
     <row r="688">
@@ -28649,7 +28649,7 @@
         <v>13</v>
       </c>
       <c r="K688" t="n">
-        <v>1.192511441987782</v>
+        <v>1.191563974902048</v>
       </c>
     </row>
     <row r="689">
@@ -28690,7 +28690,7 @@
         <v>13</v>
       </c>
       <c r="K689" t="n">
-        <v>1.192511441987782</v>
+        <v>1.191563974902048</v>
       </c>
     </row>
     <row r="690">
@@ -28731,7 +28731,7 @@
         <v>13</v>
       </c>
       <c r="K690" t="n">
-        <v>1.230191114065607</v>
+        <v>1.230980927992828</v>
       </c>
     </row>
     <row r="691">
@@ -28772,7 +28772,7 @@
         <v>13</v>
       </c>
       <c r="K691" t="n">
-        <v>1.230191114065607</v>
+        <v>1.230980927992828</v>
       </c>
     </row>
     <row r="692">
@@ -28813,7 +28813,7 @@
         <v>13</v>
       </c>
       <c r="K692" t="n">
-        <v>1.259637555553982</v>
+        <v>1.259532046255494</v>
       </c>
     </row>
     <row r="693">
@@ -28854,7 +28854,7 @@
         <v>13</v>
       </c>
       <c r="K693" t="n">
-        <v>1.259637555553982</v>
+        <v>1.259532046255494</v>
       </c>
     </row>
     <row r="694">
@@ -28895,7 +28895,7 @@
         <v>13</v>
       </c>
       <c r="K694" t="n">
-        <v>1.259637555553982</v>
+        <v>1.259532046255494</v>
       </c>
     </row>
     <row r="695">
@@ -28936,7 +28936,7 @@
         <v>13</v>
       </c>
       <c r="K695" t="n">
-        <v>1.238217641228388</v>
+        <v>1.236068655839659</v>
       </c>
     </row>
     <row r="696">
@@ -28977,7 +28977,7 @@
         <v>13</v>
       </c>
       <c r="K696" t="n">
-        <v>1.271140958094805</v>
+        <v>1.270137853290878</v>
       </c>
     </row>
     <row r="697">
@@ -29018,7 +29018,7 @@
         <v>13</v>
       </c>
       <c r="K697" t="n">
-        <v>1.271140958094805</v>
+        <v>1.270137853290878</v>
       </c>
     </row>
     <row r="698">
@@ -29059,7 +29059,7 @@
         <v>13</v>
       </c>
       <c r="K698" t="n">
-        <v>1.271140958094805</v>
+        <v>1.270137853290878</v>
       </c>
     </row>
     <row r="699">
@@ -29100,7 +29100,7 @@
         <v>13</v>
       </c>
       <c r="K699" t="n">
-        <v>1.246476226299253</v>
+        <v>1.247018149666676</v>
       </c>
     </row>
     <row r="700">
@@ -29141,7 +29141,7 @@
         <v>13</v>
       </c>
       <c r="K700" t="n">
-        <v>1.21424434546696</v>
+        <v>1.215000827949028</v>
       </c>
     </row>
     <row r="701">
@@ -29182,7 +29182,7 @@
         <v>13</v>
       </c>
       <c r="K701" t="n">
-        <v>1.08240830726112</v>
+        <v>1.082121530200917</v>
       </c>
     </row>
     <row r="702">
@@ -29223,7 +29223,7 @@
         <v>13</v>
       </c>
       <c r="K702" t="n">
-        <v>1.08240830726112</v>
+        <v>1.082121530200917</v>
       </c>
     </row>
     <row r="703">
@@ -29264,7 +29264,7 @@
         <v>13</v>
       </c>
       <c r="K703" t="n">
-        <v>1.353934259446763</v>
+        <v>1.351905327432936</v>
       </c>
     </row>
     <row r="704">
@@ -29305,7 +29305,7 @@
         <v>13</v>
       </c>
       <c r="K704" t="n">
-        <v>1.539083828655332</v>
+        <v>1.537489398355154</v>
       </c>
     </row>
     <row r="705">
@@ -29346,7 +29346,7 @@
         <v>13</v>
       </c>
       <c r="K705" t="n">
-        <v>1.707101891362171</v>
+        <v>1.706649683768364</v>
       </c>
     </row>
     <row r="706">
@@ -29387,7 +29387,7 @@
         <v>13</v>
       </c>
       <c r="K706" t="n">
-        <v>1.707101891362171</v>
+        <v>1.706649683768364</v>
       </c>
     </row>
     <row r="707">
@@ -29428,7 +29428,7 @@
         <v>13</v>
       </c>
       <c r="K707" t="n">
-        <v>1.760866169857994</v>
+        <v>1.760281962729923</v>
       </c>
     </row>
     <row r="708">
@@ -29469,7 +29469,7 @@
         <v>13</v>
       </c>
       <c r="K708" t="n">
-        <v>1.800454144468452</v>
+        <v>1.800443189606836</v>
       </c>
     </row>
     <row r="709">
@@ -29510,7 +29510,7 @@
         <v>13</v>
       </c>
       <c r="K709" t="n">
-        <v>1.773798350279864</v>
+        <v>1.774404939972171</v>
       </c>
     </row>
     <row r="710">
@@ -29551,7 +29551,7 @@
         <v>13</v>
       </c>
       <c r="K710" t="n">
-        <v>1.750849390179793</v>
+        <v>1.752084799236991</v>
       </c>
     </row>
     <row r="711">
@@ -29592,7 +29592,7 @@
         <v>13</v>
       </c>
       <c r="K711" t="n">
-        <v>1.714611439875289</v>
+        <v>1.715495438880998</v>
       </c>
     </row>
     <row r="712">
@@ -29633,7 +29633,7 @@
         <v>13</v>
       </c>
       <c r="K712" t="n">
-        <v>1.675320824652536</v>
+        <v>1.675801451262693</v>
       </c>
     </row>
     <row r="713">
@@ -29674,7 +29674,7 @@
         <v>13</v>
       </c>
       <c r="K713" t="n">
-        <v>1.641011419848974</v>
+        <v>1.641520237081376</v>
       </c>
     </row>
     <row r="714">
@@ -29715,7 +29715,7 @@
         <v>13</v>
       </c>
       <c r="K714" t="n">
-        <v>1.641011419848974</v>
+        <v>1.641520237081376</v>
       </c>
     </row>
     <row r="715">
@@ -29756,7 +29756,7 @@
         <v>13</v>
       </c>
       <c r="K715" t="n">
-        <v>1.529693668240978</v>
+        <v>1.530027453887061</v>
       </c>
     </row>
     <row r="716">
@@ -29797,7 +29797,7 @@
         <v>13</v>
       </c>
       <c r="K716" t="n">
-        <v>1.529558360161705</v>
+        <v>1.529307063530011</v>
       </c>
     </row>
     <row r="717">
@@ -29838,7 +29838,7 @@
         <v>13</v>
       </c>
       <c r="K717" t="n">
-        <v>1.571086936145376</v>
+        <v>1.571037764628567</v>
       </c>
     </row>
     <row r="718">
@@ -29879,7 +29879,7 @@
         <v>13</v>
       </c>
       <c r="K718" t="n">
-        <v>1.572805434105391</v>
+        <v>1.572603315557842</v>
       </c>
     </row>
     <row r="719">
@@ -29920,7 +29920,7 @@
         <v>13</v>
       </c>
       <c r="K719" t="n">
-        <v>1.714043363986851</v>
+        <v>1.712698358872079</v>
       </c>
     </row>
     <row r="720">
@@ -29961,7 +29961,7 @@
         <v>13</v>
       </c>
       <c r="K720" t="n">
-        <v>1.775630120058691</v>
+        <v>1.774620569285286</v>
       </c>
     </row>
     <row r="721">
@@ -30002,7 +30002,7 @@
         <v>13</v>
       </c>
       <c r="K721" t="n">
-        <v>1.917274855126093</v>
+        <v>1.916506431773018</v>
       </c>
     </row>
     <row r="722">
@@ -30043,7 +30043,7 @@
         <v>13</v>
       </c>
       <c r="K722" t="n">
-        <v>1.95549623144374</v>
+        <v>1.955421817642695</v>
       </c>
     </row>
     <row r="723">
@@ -30084,7 +30084,7 @@
         <v>13</v>
       </c>
       <c r="K723" t="n">
-        <v>1.962587395964982</v>
+        <v>1.962363337630874</v>
       </c>
     </row>
     <row r="724">
@@ -30125,7 +30125,7 @@
         <v>13</v>
       </c>
       <c r="K724" t="n">
-        <v>1.962587395964982</v>
+        <v>1.962363337630874</v>
       </c>
     </row>
     <row r="725">
@@ -30166,7 +30166,7 @@
         <v>13</v>
       </c>
       <c r="K725" t="n">
-        <v>1.98467417637582</v>
+        <v>1.984837551144464</v>
       </c>
     </row>
     <row r="726">
@@ -30207,7 +30207,7 @@
         <v>13</v>
       </c>
       <c r="K726" t="n">
-        <v>1.984499560046709</v>
+        <v>1.985067383381825</v>
       </c>
     </row>
     <row r="727">
@@ -30248,7 +30248,7 @@
         <v>13</v>
       </c>
       <c r="K727" t="n">
-        <v>1.996816372769612</v>
+        <v>1.998405598061372</v>
       </c>
     </row>
     <row r="728">
@@ -30289,7 +30289,7 @@
         <v>13</v>
       </c>
       <c r="K728" t="n">
-        <v>1.792757889928098</v>
+        <v>1.795674284414628</v>
       </c>
     </row>
     <row r="729">
@@ -30330,7 +30330,7 @@
         <v>13</v>
       </c>
       <c r="K729" t="n">
-        <v>1.792757889928098</v>
+        <v>1.795674284414628</v>
       </c>
     </row>
     <row r="730">
@@ -30371,7 +30371,7 @@
         <v>13</v>
       </c>
       <c r="K730" t="n">
-        <v>1.792757889928098</v>
+        <v>1.795674284414628</v>
       </c>
     </row>
     <row r="731">
@@ -30412,7 +30412,7 @@
         <v>13</v>
       </c>
       <c r="K731" t="n">
-        <v>1.792757889928098</v>
+        <v>1.795674284414628</v>
       </c>
     </row>
     <row r="732">
@@ -30453,7 +30453,7 @@
         <v>13</v>
       </c>
       <c r="K732" t="n">
-        <v>1.612042480756106</v>
+        <v>1.621470094764107</v>
       </c>
     </row>
     <row r="733">
@@ -30494,7 +30494,7 @@
         <v>13</v>
       </c>
       <c r="K733" t="n">
-        <v>1.297147213398316</v>
+        <v>1.306700516551152</v>
       </c>
     </row>
     <row r="734">
@@ -30535,7 +30535,7 @@
         <v>13</v>
       </c>
       <c r="K734" t="n">
-        <v>0.7067136403301323</v>
+        <v>0.7087162214950372</v>
       </c>
     </row>
     <row r="735">
@@ -30576,7 +30576,7 @@
         <v>13</v>
       </c>
       <c r="K735" t="n">
-        <v>0.5871130954069996</v>
+        <v>0.5888286666773458</v>
       </c>
     </row>
     <row r="736">
@@ -30617,7 +30617,7 @@
         <v>13</v>
       </c>
       <c r="K736" t="n">
-        <v>0.4940409357744504</v>
+        <v>0.494852414325166</v>
       </c>
     </row>
     <row r="737">
@@ -30658,7 +30658,7 @@
         <v>13</v>
       </c>
       <c r="K737" t="n">
-        <v>0.5821738416624168</v>
+        <v>0.580762052037825</v>
       </c>
     </row>
     <row r="738">
@@ -30699,7 +30699,7 @@
         <v>13</v>
       </c>
       <c r="K738" t="n">
-        <v>0.78150465117247</v>
+        <v>0.7796748849414821</v>
       </c>
     </row>
     <row r="739">
@@ -30740,7 +30740,7 @@
         <v>13</v>
       </c>
       <c r="K739" t="n">
-        <v>0.9278436477286818</v>
+        <v>0.9253699918221164</v>
       </c>
     </row>
     <row r="740">
@@ -30781,7 +30781,7 @@
         <v>13</v>
       </c>
       <c r="K740" t="n">
-        <v>1.406594807233208</v>
+        <v>1.404484275595463</v>
       </c>
     </row>
     <row r="741">
@@ -30822,7 +30822,7 @@
         <v>13</v>
       </c>
       <c r="K741" t="n">
-        <v>1.581488928685644</v>
+        <v>1.580414296818767</v>
       </c>
     </row>
     <row r="742">
@@ -30863,7 +30863,7 @@
         <v>13</v>
       </c>
       <c r="K742" t="n">
-        <v>1.687822216721761</v>
+        <v>1.687498212251682</v>
       </c>
     </row>
     <row r="743">
@@ -30904,7 +30904,7 @@
         <v>13</v>
       </c>
       <c r="K743" t="n">
-        <v>1.71206007924712</v>
+        <v>1.711612073262385</v>
       </c>
     </row>
     <row r="744">
@@ -30945,7 +30945,7 @@
         <v>13</v>
       </c>
       <c r="K744" t="n">
-        <v>1.686709531300954</v>
+        <v>1.687914846699695</v>
       </c>
     </row>
     <row r="745">
@@ -30986,7 +30986,7 @@
         <v>13</v>
       </c>
       <c r="K745" t="n">
-        <v>1.610263445549494</v>
+        <v>1.613910601793393</v>
       </c>
     </row>
     <row r="746">
@@ -31027,7 +31027,7 @@
         <v>13</v>
       </c>
       <c r="K746" t="n">
-        <v>1.610263445549494</v>
+        <v>1.613910601793393</v>
       </c>
     </row>
     <row r="747">
@@ -31068,7 +31068,7 @@
         <v>13</v>
       </c>
       <c r="K747" t="n">
-        <v>1.511280420782374</v>
+        <v>1.516832217295998</v>
       </c>
     </row>
     <row r="748">
@@ -31109,7 +31109,7 @@
         <v>13</v>
       </c>
       <c r="K748" t="n">
-        <v>1.191151002679151</v>
+        <v>1.1905287640164</v>
       </c>
     </row>
     <row r="749">
@@ -31150,7 +31150,7 @@
         <v>13</v>
       </c>
       <c r="K749" t="n">
-        <v>1.057007068759942</v>
+        <v>1.058441617567214</v>
       </c>
     </row>
     <row r="750">
@@ -31191,7 +31191,7 @@
         <v>13</v>
       </c>
       <c r="K750" t="n">
-        <v>1.057007068759942</v>
+        <v>1.058441617567214</v>
       </c>
     </row>
     <row r="751">
@@ -31232,7 +31232,7 @@
         <v>13</v>
       </c>
       <c r="K751" t="n">
-        <v>0.9802622604953638</v>
+        <v>0.9802377354462499</v>
       </c>
     </row>
     <row r="752">
@@ -31273,7 +31273,7 @@
         <v>13</v>
       </c>
       <c r="K752" t="n">
-        <v>0.8381688988038087</v>
+        <v>0.8376516339485338</v>
       </c>
     </row>
     <row r="753">
@@ -31314,7 +31314,7 @@
         <v>13</v>
       </c>
       <c r="K753" t="n">
-        <v>0.4728001678573671</v>
+        <v>0.4730533437154759</v>
       </c>
     </row>
   </sheetData>
